--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI197"/>
+  <dimension ref="A1:AI198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22326,6 +22326,117 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>313.88</v>
+      </c>
+      <c r="C198" t="n">
+        <v>322.44</v>
+      </c>
+      <c r="D198" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="E198" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="F198" t="n">
+        <v>351.74</v>
+      </c>
+      <c r="G198" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="H198" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="I198" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="J198" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="K198" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="L198" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="M198" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="N198" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="O198" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="P198" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>337.63</v>
+      </c>
+      <c r="R198" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="S198" t="n">
+        <v>336.42</v>
+      </c>
+      <c r="T198" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="U198" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="V198" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="W198" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="X198" t="n">
+        <v>347.24</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>334.62</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>334.99</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>337.92</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>344.33</v>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22337,7 +22448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24310,6 +24421,16 @@
       </c>
       <c r="B197" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>
@@ -24478,28 +24599,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1740096291236018</v>
+        <v>-0.1810845552692252</v>
       </c>
       <c r="J2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003916678644445448</v>
+        <v>0.004281986573211771</v>
       </c>
       <c r="M2" t="n">
-        <v>17.65981994397778</v>
+        <v>17.61405667838656</v>
       </c>
       <c r="N2" t="n">
-        <v>458.9839044255353</v>
+        <v>456.8910468000146</v>
       </c>
       <c r="O2" t="n">
-        <v>21.423909643796</v>
+        <v>21.37500986666473</v>
       </c>
       <c r="P2" t="n">
-        <v>325.9373249439179</v>
+        <v>326.0072843513419</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24556,28 +24677,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1817748482052012</v>
+        <v>-0.1831520558657531</v>
       </c>
       <c r="J3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005612070910896549</v>
+        <v>0.005756047627322181</v>
       </c>
       <c r="M3" t="n">
-        <v>15.33827025596725</v>
+        <v>15.26877494490967</v>
       </c>
       <c r="N3" t="n">
-        <v>353.4765435209343</v>
+        <v>351.6654985978396</v>
       </c>
       <c r="O3" t="n">
-        <v>18.80097187703163</v>
+        <v>18.75274642813259</v>
       </c>
       <c r="P3" t="n">
-        <v>328.6975729291128</v>
+        <v>328.7110425157651</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24634,28 +24755,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3069984805429396</v>
+        <v>-0.3041072476952313</v>
       </c>
       <c r="J4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01975662996713501</v>
+        <v>0.01958911877874614</v>
       </c>
       <c r="M4" t="n">
-        <v>14.2420788610705</v>
+        <v>14.18012191743133</v>
       </c>
       <c r="N4" t="n">
-        <v>282.3279171656978</v>
+        <v>280.9210944306951</v>
       </c>
       <c r="O4" t="n">
-        <v>16.8026163785792</v>
+        <v>16.7607008931815</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8221949758486</v>
+        <v>334.7939176778856</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24712,28 +24833,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3449966038525275</v>
+        <v>-0.3392854025209296</v>
       </c>
       <c r="J5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03246338342413979</v>
+        <v>0.03172032532514124</v>
       </c>
       <c r="M5" t="n">
-        <v>12.4431809963526</v>
+        <v>12.40070100382339</v>
       </c>
       <c r="N5" t="n">
-        <v>217.2898159749876</v>
+        <v>216.3684601945573</v>
       </c>
       <c r="O5" t="n">
-        <v>14.74075357554652</v>
+        <v>14.70946838585805</v>
       </c>
       <c r="P5" t="n">
-        <v>344.0221302229082</v>
+        <v>343.9669518745939</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24790,28 +24911,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4184036287985082</v>
+        <v>-0.4126720845890803</v>
       </c>
       <c r="J6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K6" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05221416984058225</v>
+        <v>0.05131912150264861</v>
       </c>
       <c r="M6" t="n">
-        <v>11.50437229268295</v>
+        <v>11.46741396681104</v>
       </c>
       <c r="N6" t="n">
-        <v>194.6474966259537</v>
+        <v>193.8436323059832</v>
       </c>
       <c r="O6" t="n">
-        <v>13.95161268907482</v>
+        <v>13.92277387254362</v>
       </c>
       <c r="P6" t="n">
-        <v>356.5468174933188</v>
+        <v>356.4914426037982</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24868,28 +24989,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3836819384598942</v>
+        <v>-0.3788033289754343</v>
       </c>
       <c r="J7" t="n">
+        <v>197</v>
+      </c>
+      <c r="K7" t="n">
         <v>196</v>
       </c>
-      <c r="K7" t="n">
-        <v>195</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05432428788305421</v>
+        <v>0.05349635078123183</v>
       </c>
       <c r="M7" t="n">
-        <v>10.20887818019179</v>
+        <v>10.17414110698416</v>
       </c>
       <c r="N7" t="n">
-        <v>156.6296740956388</v>
+        <v>155.9722036283331</v>
       </c>
       <c r="O7" t="n">
-        <v>12.51517774926265</v>
+        <v>12.48888320180524</v>
       </c>
       <c r="P7" t="n">
-        <v>369.5157316948347</v>
+        <v>369.46846330467</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24946,28 +25067,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3478064729212383</v>
+        <v>-0.3456478451708858</v>
       </c>
       <c r="J8" t="n">
+        <v>197</v>
+      </c>
+      <c r="K8" t="n">
         <v>196</v>
       </c>
-      <c r="K8" t="n">
-        <v>195</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05346809115807893</v>
+        <v>0.0533469948268579</v>
       </c>
       <c r="M8" t="n">
-        <v>9.298742513003788</v>
+        <v>9.259573659068199</v>
       </c>
       <c r="N8" t="n">
-        <v>130.8877613801484</v>
+        <v>130.2477006619719</v>
       </c>
       <c r="O8" t="n">
-        <v>11.44061892469758</v>
+        <v>11.41261147424076</v>
       </c>
       <c r="P8" t="n">
-        <v>386.5039325539978</v>
+        <v>386.4830178119901</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25024,28 +25145,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2578779896403492</v>
+        <v>-0.2564730564844505</v>
       </c>
       <c r="J9" t="n">
+        <v>197</v>
+      </c>
+      <c r="K9" t="n">
         <v>196</v>
       </c>
-      <c r="K9" t="n">
-        <v>195</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03355005949845424</v>
+        <v>0.0335255023673473</v>
       </c>
       <c r="M9" t="n">
-        <v>8.996066666662381</v>
+        <v>8.956611611087263</v>
       </c>
       <c r="N9" t="n">
-        <v>117.0840565294355</v>
+        <v>116.4984370053967</v>
       </c>
       <c r="O9" t="n">
-        <v>10.82053864322084</v>
+        <v>10.79344416789176</v>
       </c>
       <c r="P9" t="n">
-        <v>395.5029624672802</v>
+        <v>395.4893502015763</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25102,28 +25223,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2159077989394101</v>
+        <v>-0.2166699926137516</v>
       </c>
       <c r="J10" t="n">
+        <v>197</v>
+      </c>
+      <c r="K10" t="n">
         <v>196</v>
       </c>
-      <c r="K10" t="n">
-        <v>195</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02756642610390703</v>
+        <v>0.02803351085166461</v>
       </c>
       <c r="M10" t="n">
-        <v>7.965985444213048</v>
+        <v>7.930025625315953</v>
       </c>
       <c r="N10" t="n">
-        <v>100.5076872894109</v>
+        <v>99.99835066729847</v>
       </c>
       <c r="O10" t="n">
-        <v>10.02535222769808</v>
+        <v>9.999917533024883</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0616008692905</v>
+        <v>385.0689856923829</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25180,28 +25301,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2641263855156403</v>
+        <v>-0.2653287889007861</v>
       </c>
       <c r="J11" t="n">
+        <v>197</v>
+      </c>
+      <c r="K11" t="n">
         <v>196</v>
       </c>
-      <c r="K11" t="n">
-        <v>195</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0469743999382769</v>
+        <v>0.04784388179530552</v>
       </c>
       <c r="M11" t="n">
-        <v>7.136086911757633</v>
+        <v>7.105197149117816</v>
       </c>
       <c r="N11" t="n">
-        <v>86.50675915821418</v>
+        <v>86.07400326564274</v>
       </c>
       <c r="O11" t="n">
-        <v>9.300900986367621</v>
+        <v>9.2776076261956</v>
       </c>
       <c r="P11" t="n">
-        <v>377.7803874599895</v>
+        <v>377.7920374337218</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25258,28 +25379,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2640638733198111</v>
+        <v>-0.2651690571011047</v>
       </c>
       <c r="J12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04903278575285863</v>
+        <v>0.04990225527990122</v>
       </c>
       <c r="M12" t="n">
-        <v>7.070537558312807</v>
+        <v>7.040169899559136</v>
       </c>
       <c r="N12" t="n">
-        <v>83.67611403595528</v>
+        <v>83.25875172933274</v>
       </c>
       <c r="O12" t="n">
-        <v>9.147464896677947</v>
+        <v>9.124623374656773</v>
       </c>
       <c r="P12" t="n">
-        <v>370.7720873724756</v>
+        <v>370.7826794217937</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25336,28 +25457,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2563839859019175</v>
+        <v>-0.2584562603992993</v>
       </c>
       <c r="J13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04974318982655301</v>
+        <v>0.05098626755109481</v>
       </c>
       <c r="M13" t="n">
-        <v>6.979930454524128</v>
+        <v>6.954894682230448</v>
       </c>
       <c r="N13" t="n">
-        <v>77.69511211157025</v>
+        <v>77.32670091231739</v>
       </c>
       <c r="O13" t="n">
-        <v>8.81448308816633</v>
+        <v>8.793560195524757</v>
       </c>
       <c r="P13" t="n">
-        <v>364.8677150792289</v>
+        <v>364.8875756979317</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25414,28 +25535,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1379745719762361</v>
+        <v>-0.1422232177872934</v>
       </c>
       <c r="J14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01829606719153465</v>
+        <v>0.0195803393911671</v>
       </c>
       <c r="M14" t="n">
-        <v>6.462654006710618</v>
+        <v>6.455783235508922</v>
       </c>
       <c r="N14" t="n">
-        <v>63.20121733789373</v>
+        <v>62.98960573730788</v>
       </c>
       <c r="O14" t="n">
-        <v>7.949919329017982</v>
+        <v>7.93659912918045</v>
       </c>
       <c r="P14" t="n">
-        <v>359.4596556467196</v>
+        <v>359.5003745449944</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25492,28 +25613,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1323997059089585</v>
+        <v>-0.1375633199139083</v>
       </c>
       <c r="J15" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K15" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01627049287250937</v>
+        <v>0.01767585282362583</v>
       </c>
       <c r="M15" t="n">
-        <v>6.74002153154203</v>
+        <v>6.737427247668467</v>
       </c>
       <c r="N15" t="n">
-        <v>65.57730707109458</v>
+        <v>65.4057353794728</v>
       </c>
       <c r="O15" t="n">
-        <v>8.097981666507685</v>
+        <v>8.087381243608638</v>
       </c>
       <c r="P15" t="n">
-        <v>358.1570663756926</v>
+        <v>358.2065543026105</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25570,28 +25691,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09207042135118793</v>
+        <v>-0.1016052388079624</v>
       </c>
       <c r="J16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L16" t="n">
-        <v>0.009335007153703057</v>
+        <v>0.01134938393852847</v>
       </c>
       <c r="M16" t="n">
-        <v>6.246867237208418</v>
+        <v>6.266736249081787</v>
       </c>
       <c r="N16" t="n">
-        <v>55.66176469048023</v>
+        <v>55.92923102219226</v>
       </c>
       <c r="O16" t="n">
-        <v>7.460681248416945</v>
+        <v>7.478584827505285</v>
       </c>
       <c r="P16" t="n">
-        <v>357.5912168754871</v>
+        <v>357.6825982895556</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25648,28 +25769,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09197085209357148</v>
+        <v>-0.1031902338590344</v>
       </c>
       <c r="J17" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K17" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009523334794114269</v>
+        <v>0.01191497769160932</v>
       </c>
       <c r="M17" t="n">
-        <v>6.031607064624133</v>
+        <v>6.065136406872294</v>
       </c>
       <c r="N17" t="n">
-        <v>54.43273605537328</v>
+        <v>54.9179565387069</v>
       </c>
       <c r="O17" t="n">
-        <v>7.377854434412032</v>
+        <v>7.410665053738895</v>
       </c>
       <c r="P17" t="n">
-        <v>352.3880416216499</v>
+        <v>352.4955678512134</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25726,28 +25847,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0325125607635461</v>
+        <v>-0.04103135710381659</v>
       </c>
       <c r="J18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001237636173150203</v>
+        <v>0.001973459163947089</v>
       </c>
       <c r="M18" t="n">
-        <v>5.951286619749078</v>
+        <v>5.964824928652831</v>
       </c>
       <c r="N18" t="n">
-        <v>52.78081308530495</v>
+        <v>52.95193104056784</v>
       </c>
       <c r="O18" t="n">
-        <v>7.26504047375546</v>
+        <v>7.276807750694521</v>
       </c>
       <c r="P18" t="n">
-        <v>347.6493035575014</v>
+        <v>347.7309474546464</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25804,28 +25925,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0322509254988141</v>
+        <v>0.02472895844824177</v>
       </c>
       <c r="J19" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K19" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0009330578121616862</v>
+        <v>0.0005516712273108126</v>
       </c>
       <c r="M19" t="n">
-        <v>6.761932878789894</v>
+        <v>6.76153796541838</v>
       </c>
       <c r="N19" t="n">
-        <v>68.90884137294422</v>
+        <v>68.90135378975212</v>
       </c>
       <c r="O19" t="n">
-        <v>8.301134944870142</v>
+        <v>8.300683935059334</v>
       </c>
       <c r="P19" t="n">
-        <v>343.8490678314789</v>
+        <v>343.9211581456118</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -25882,28 +26003,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01828168416067923</v>
+        <v>0.006241055044775185</v>
       </c>
       <c r="J20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0002244573463303645</v>
+        <v>2.618233989648555e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>7.681597108808437</v>
+        <v>7.690936595191657</v>
       </c>
       <c r="N20" t="n">
-        <v>92.10975686016208</v>
+        <v>92.51929003928528</v>
       </c>
       <c r="O20" t="n">
-        <v>9.59738281304659</v>
+        <v>9.618694819947521</v>
       </c>
       <c r="P20" t="n">
-        <v>345.0112753714621</v>
+        <v>345.1266724118223</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -25960,28 +26081,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02378751060205156</v>
+        <v>0.01346554460552195</v>
       </c>
       <c r="J21" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K21" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0003899588522724429</v>
+        <v>0.0001253722512931654</v>
       </c>
       <c r="M21" t="n">
-        <v>7.423910427463838</v>
+        <v>7.427656280897486</v>
       </c>
       <c r="N21" t="n">
-        <v>89.74584776826443</v>
+        <v>89.93485988767179</v>
       </c>
       <c r="O21" t="n">
-        <v>9.473428511804183</v>
+        <v>9.483399173696728</v>
       </c>
       <c r="P21" t="n">
-        <v>347.8219869782347</v>
+        <v>347.9209124010869</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26038,28 +26159,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.06595291337171232</v>
+        <v>-0.06812939134186574</v>
       </c>
       <c r="J22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002384821008386773</v>
+        <v>0.002569844720444525</v>
       </c>
       <c r="M22" t="n">
-        <v>7.81531755546357</v>
+        <v>7.786123608201703</v>
       </c>
       <c r="N22" t="n">
-        <v>112.5848042440535</v>
+        <v>112.0419665113419</v>
       </c>
       <c r="O22" t="n">
-        <v>10.61059867510092</v>
+        <v>10.58498778985322</v>
       </c>
       <c r="P22" t="n">
-        <v>353.9955087648493</v>
+        <v>354.0163680666139</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26116,28 +26237,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07353723019024258</v>
+        <v>-0.07856967274526187</v>
       </c>
       <c r="J23" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K23" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002721319035721037</v>
+        <v>0.003133228023670109</v>
       </c>
       <c r="M23" t="n">
-        <v>8.117701718519955</v>
+        <v>8.099882325449096</v>
       </c>
       <c r="N23" t="n">
-        <v>122.618545345201</v>
+        <v>122.1493328885828</v>
       </c>
       <c r="O23" t="n">
-        <v>11.07332584841614</v>
+        <v>11.05211893206831</v>
       </c>
       <c r="P23" t="n">
-        <v>360.4631209560337</v>
+        <v>360.5113517395784</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -26194,28 +26315,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0642807961709866</v>
+        <v>-0.07320156726493032</v>
       </c>
       <c r="J24" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K24" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001885427126015693</v>
+        <v>0.002459969035514376</v>
       </c>
       <c r="M24" t="n">
-        <v>8.753021792416826</v>
+        <v>8.75394315222343</v>
       </c>
       <c r="N24" t="n">
-        <v>135.3435887782493</v>
+        <v>135.138017783561</v>
       </c>
       <c r="O24" t="n">
-        <v>11.63372634963748</v>
+        <v>11.62488786111767</v>
       </c>
       <c r="P24" t="n">
-        <v>358.7434391379591</v>
+        <v>358.8289355494891</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -26272,28 +26393,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.03276410363380232</v>
+        <v>-0.04369324142499616</v>
       </c>
       <c r="J25" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K25" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0004693329411149527</v>
+        <v>0.000838629110738065</v>
       </c>
       <c r="M25" t="n">
-        <v>9.016919938979681</v>
+        <v>9.024535986919012</v>
       </c>
       <c r="N25" t="n">
-        <v>141.4543203539897</v>
+        <v>141.4589152551378</v>
       </c>
       <c r="O25" t="n">
-        <v>11.89345703964956</v>
+        <v>11.89365020736434</v>
       </c>
       <c r="P25" t="n">
-        <v>353.2712938822327</v>
+        <v>353.3760384219618</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -26350,28 +26471,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0474785444596864</v>
+        <v>0.03508735113008979</v>
       </c>
       <c r="J26" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K26" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0006964947820281564</v>
+        <v>0.0003826315679402725</v>
       </c>
       <c r="M26" t="n">
-        <v>10.45802926084863</v>
+        <v>10.46281378772971</v>
       </c>
       <c r="N26" t="n">
-        <v>200.114650457904</v>
+        <v>200.0277524046374</v>
       </c>
       <c r="O26" t="n">
-        <v>14.14618854878953</v>
+        <v>14.1431167853708</v>
       </c>
       <c r="P26" t="n">
-        <v>347.1301507467832</v>
+        <v>347.2489075844037</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -26428,28 +26549,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2011102281618495</v>
+        <v>0.1886315441482783</v>
       </c>
       <c r="J27" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K27" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01008294354431538</v>
+        <v>0.008937601663117523</v>
       </c>
       <c r="M27" t="n">
-        <v>11.65363273206155</v>
+        <v>11.65501125887426</v>
       </c>
       <c r="N27" t="n">
-        <v>245.6882219878953</v>
+        <v>245.3831498884983</v>
       </c>
       <c r="O27" t="n">
-        <v>15.6744448701667</v>
+        <v>15.66471033528862</v>
       </c>
       <c r="P27" t="n">
-        <v>343.0550765186644</v>
+        <v>343.1746718644636</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -26506,28 +26627,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3268239141658442</v>
+        <v>0.3116725743509688</v>
       </c>
       <c r="J28" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K28" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02777583022460273</v>
+        <v>0.02542804468285875</v>
       </c>
       <c r="M28" t="n">
-        <v>11.67138949336976</v>
+        <v>11.68395354538597</v>
       </c>
       <c r="N28" t="n">
-        <v>231.3297916707411</v>
+        <v>231.5443634430613</v>
       </c>
       <c r="O28" t="n">
-        <v>15.20952963344827</v>
+        <v>15.21658185806068</v>
       </c>
       <c r="P28" t="n">
-        <v>342.0008401975001</v>
+        <v>342.1460501990122</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -26584,28 +26705,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3004827647457737</v>
+        <v>0.2844806559511031</v>
       </c>
       <c r="J29" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K29" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02127119618868467</v>
+        <v>0.01918673538068405</v>
       </c>
       <c r="M29" t="n">
-        <v>12.27826240553252</v>
+        <v>12.2849329285509</v>
       </c>
       <c r="N29" t="n">
-        <v>257.0479459580748</v>
+        <v>257.2923177213002</v>
       </c>
       <c r="O29" t="n">
-        <v>16.03271486548909</v>
+        <v>16.04033409007743</v>
       </c>
       <c r="P29" t="n">
-        <v>344.6921846064541</v>
+        <v>344.8455483532029</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -26662,28 +26783,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3551689943509859</v>
+        <v>0.3403652119063129</v>
       </c>
       <c r="J30" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02938705830858923</v>
+        <v>0.02718704865825072</v>
       </c>
       <c r="M30" t="n">
-        <v>12.29861311213252</v>
+        <v>12.29662518179479</v>
       </c>
       <c r="N30" t="n">
-        <v>257.7891309261211</v>
+        <v>257.8064050352955</v>
       </c>
       <c r="O30" t="n">
-        <v>16.05581299486641</v>
+        <v>16.05635092526616</v>
       </c>
       <c r="P30" t="n">
-        <v>348.5803663575405</v>
+        <v>348.7222453792931</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -26740,28 +26861,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3022494185220487</v>
+        <v>0.2876736436976781</v>
       </c>
       <c r="J31" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K31" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02086481487091429</v>
+        <v>0.01903815554963439</v>
       </c>
       <c r="M31" t="n">
-        <v>12.32531923482962</v>
+        <v>12.31817960873703</v>
       </c>
       <c r="N31" t="n">
-        <v>265.2550236670622</v>
+        <v>265.193872971772</v>
       </c>
       <c r="O31" t="n">
-        <v>16.28665170214744</v>
+        <v>16.2847742683702</v>
       </c>
       <c r="P31" t="n">
-        <v>348.2228482816766</v>
+        <v>348.3625420850067</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -26818,28 +26939,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3040763467538367</v>
+        <v>0.2880460756265271</v>
       </c>
       <c r="J32" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K32" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L32" t="n">
-        <v>0.02025909831253569</v>
+        <v>0.01829962824468812</v>
       </c>
       <c r="M32" t="n">
-        <v>12.6491941031308</v>
+        <v>12.64249840358365</v>
       </c>
       <c r="N32" t="n">
-        <v>276.6692884524991</v>
+        <v>276.8195171502338</v>
       </c>
       <c r="O32" t="n">
-        <v>16.63337874433511</v>
+        <v>16.63789401187043</v>
       </c>
       <c r="P32" t="n">
-        <v>347.5586359216473</v>
+        <v>347.7122695753756</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -26896,28 +27017,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2993965112569313</v>
+        <v>0.2831525626485371</v>
       </c>
       <c r="J33" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K33" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01975706734343385</v>
+        <v>0.01778523003997035</v>
       </c>
       <c r="M33" t="n">
-        <v>12.51264198493423</v>
+        <v>12.51519979614111</v>
       </c>
       <c r="N33" t="n">
-        <v>275.1751795986694</v>
+        <v>275.3747143998716</v>
       </c>
       <c r="O33" t="n">
-        <v>16.58840497451968</v>
+        <v>16.59441816997124</v>
       </c>
       <c r="P33" t="n">
-        <v>350.295557458644</v>
+        <v>350.4512389911559</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -26974,28 +27095,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2404769443163716</v>
+        <v>0.2243599879549384</v>
       </c>
       <c r="J34" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K34" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01214847525877549</v>
+        <v>0.01064186961617131</v>
       </c>
       <c r="M34" t="n">
-        <v>13.26148996853194</v>
+        <v>13.25623810269711</v>
       </c>
       <c r="N34" t="n">
-        <v>290.9519945650683</v>
+        <v>291.0465814227833</v>
       </c>
       <c r="O34" t="n">
-        <v>17.05731498698046</v>
+        <v>17.06008738027984</v>
       </c>
       <c r="P34" t="n">
-        <v>355.7307480679781</v>
+        <v>355.8852125104769</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -27033,7 +27154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI197"/>
+  <dimension ref="A1:AI198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61829,6 +61950,183 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>-34.4262779586685,172.96361773499743</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>-34.42618832121405,172.9645143761909</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>-34.42610914354508,172.96541122602983</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-34.42599488957396,172.9663073714596</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-34.425886767208375,172.967203638505</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-34.42575718428834,172.96809947352614</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-34.425610159875156,172.9689850215711</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-34.42542438952982,172.9697932409437</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-34.425224608741956,172.97062572405403</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-34.42499073446354,172.97148367328478</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-34.42473947250065,172.97233202585363</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>-34.42448706098917,172.97317974515502</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-34.424217508001036,172.97401800324874</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-34.423927084500676,172.97484571266315</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>-34.42364407385737,172.9756873464067</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>-34.423327002356075,172.97651261637603</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>-34.42295980422737,172.9772928778942</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>-34.42259878160624,172.97807742308015</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>-34.42226254400992,172.9788791572517</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>-34.42185585428523,172.97963203578863</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>-34.42138707943502,172.98034186017355</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>-34.420990792511276,172.98111077563632</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>-34.420583953538234,172.98187653915744</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>-34.42014538935941,172.98261215774002</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>-34.41970173117556,172.9833341901406</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>-34.41922036447718,172.98401716795055</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>-34.418742827108915,172.98470411500415</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>-34.418253311599386,172.98537865816988</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>-34.41771887639418,172.98602302744246</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>-34.41718510520634,172.9866656551003</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>-34.41665637953372,172.9872977548678</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>-34.41610027747205,172.9878921449858</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>-34.41553402064414,172.9884734071528</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI198"/>
+  <dimension ref="A1:AI200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22437,6 +22437,228 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>315.15</v>
+      </c>
+      <c r="C199" t="n">
+        <v>324.38</v>
+      </c>
+      <c r="D199" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="E199" t="n">
+        <v>340.99</v>
+      </c>
+      <c r="F199" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="G199" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="H199" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="I199" t="n">
+        <v>390.28</v>
+      </c>
+      <c r="J199" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="K199" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="L199" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="M199" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="N199" t="n">
+        <v>351.06</v>
+      </c>
+      <c r="O199" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="P199" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>336.86</v>
+      </c>
+      <c r="R199" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="S199" t="n">
+        <v>336.47</v>
+      </c>
+      <c r="T199" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="U199" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="V199" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="W199" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="X199" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>342.35</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>343.68</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>341.69</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>345.31</v>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>316.93</v>
+      </c>
+      <c r="C200" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="D200" t="n">
+        <v>333.61</v>
+      </c>
+      <c r="E200" t="n">
+        <v>343</v>
+      </c>
+      <c r="F200" t="n">
+        <v>352.52</v>
+      </c>
+      <c r="G200" t="n">
+        <v>367.87</v>
+      </c>
+      <c r="H200" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="I200" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="J200" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="K200" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="L200" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="M200" t="n">
+        <v>358.02</v>
+      </c>
+      <c r="N200" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="O200" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="P200" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>336.86</v>
+      </c>
+      <c r="R200" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="S200" t="n">
+        <v>336.47</v>
+      </c>
+      <c r="T200" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="U200" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="V200" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="W200" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="X200" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>336.65</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>339.21</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22448,7 +22670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B198"/>
+  <dimension ref="A1:B200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24431,6 +24653,26 @@
       </c>
       <c r="B198" t="n">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -24599,28 +24841,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1810845552692252</v>
+        <v>-0.1906718688548203</v>
       </c>
       <c r="J2" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K2" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004281986573211771</v>
+        <v>0.004840349682717626</v>
       </c>
       <c r="M2" t="n">
-        <v>17.61405667838656</v>
+        <v>17.49438292595818</v>
       </c>
       <c r="N2" t="n">
-        <v>456.8910468000146</v>
+        <v>452.4810954389674</v>
       </c>
       <c r="O2" t="n">
-        <v>21.37500986666473</v>
+        <v>21.27160302936682</v>
       </c>
       <c r="P2" t="n">
-        <v>326.0072843513419</v>
+        <v>326.102443349021</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24677,28 +24919,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1831520558657531</v>
+        <v>-0.1798135043839136</v>
       </c>
       <c r="J3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005756047627322181</v>
+        <v>0.005662570203022188</v>
       </c>
       <c r="M3" t="n">
-        <v>15.26877494490967</v>
+        <v>15.12656031319516</v>
       </c>
       <c r="N3" t="n">
-        <v>351.6654985978396</v>
+        <v>348.1279656249862</v>
       </c>
       <c r="O3" t="n">
-        <v>18.75274642813259</v>
+        <v>18.65818762969722</v>
       </c>
       <c r="P3" t="n">
-        <v>328.7110425157651</v>
+        <v>328.6782496553827</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24755,28 +24997,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3041072476952313</v>
+        <v>-0.2934031031612657</v>
       </c>
       <c r="J4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01958911877874614</v>
+        <v>0.01860677108023967</v>
       </c>
       <c r="M4" t="n">
-        <v>14.18012191743133</v>
+        <v>14.0770230773347</v>
       </c>
       <c r="N4" t="n">
-        <v>280.9210944306951</v>
+        <v>278.4040584189336</v>
       </c>
       <c r="O4" t="n">
-        <v>16.7607008931815</v>
+        <v>16.68544450768195</v>
       </c>
       <c r="P4" t="n">
-        <v>334.7939176778856</v>
+        <v>334.6888095875497</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24833,28 +25075,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3392854025209296</v>
+        <v>-0.3266904554531804</v>
       </c>
       <c r="J5" t="n">
+        <v>199</v>
+      </c>
+      <c r="K5" t="n">
         <v>197</v>
       </c>
-      <c r="K5" t="n">
-        <v>195</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03172032532514124</v>
+        <v>0.02999873262210206</v>
       </c>
       <c r="M5" t="n">
-        <v>12.40070100382339</v>
+        <v>12.32093210746876</v>
       </c>
       <c r="N5" t="n">
-        <v>216.3684601945573</v>
+        <v>214.6616127876568</v>
       </c>
       <c r="O5" t="n">
-        <v>14.70946838585805</v>
+        <v>14.65133484661574</v>
       </c>
       <c r="P5" t="n">
-        <v>343.9669518745939</v>
+        <v>343.8447768232382</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24911,28 +25153,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4126720845890803</v>
+        <v>-0.4013939035875331</v>
       </c>
       <c r="J6" t="n">
+        <v>199</v>
+      </c>
+      <c r="K6" t="n">
         <v>197</v>
       </c>
-      <c r="K6" t="n">
-        <v>195</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05131912150264861</v>
+        <v>0.04954345119786163</v>
       </c>
       <c r="M6" t="n">
-        <v>11.46741396681104</v>
+        <v>11.39357363672015</v>
       </c>
       <c r="N6" t="n">
-        <v>193.8436323059832</v>
+        <v>192.2647448683586</v>
       </c>
       <c r="O6" t="n">
-        <v>13.92277387254362</v>
+        <v>13.8659563272195</v>
       </c>
       <c r="P6" t="n">
-        <v>356.4914426037982</v>
+        <v>356.3820429387378</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24989,28 +25231,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3788033289754343</v>
+        <v>-0.3658695224294126</v>
       </c>
       <c r="J7" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K7" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05349635078123183</v>
+        <v>0.05089158191267296</v>
       </c>
       <c r="M7" t="n">
-        <v>10.17414110698416</v>
+        <v>10.11648260897359</v>
       </c>
       <c r="N7" t="n">
-        <v>155.9722036283331</v>
+        <v>154.919691188377</v>
       </c>
       <c r="O7" t="n">
-        <v>12.48888320180524</v>
+        <v>12.44667390062008</v>
       </c>
       <c r="P7" t="n">
-        <v>369.46846330467</v>
+        <v>369.3426426498118</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25067,28 +25309,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3456478451708858</v>
+        <v>-0.3406599105237517</v>
       </c>
       <c r="J8" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K8" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0533469948268579</v>
+        <v>0.05286885696276378</v>
       </c>
       <c r="M8" t="n">
-        <v>9.259573659068199</v>
+        <v>9.185250790370672</v>
       </c>
       <c r="N8" t="n">
-        <v>130.2477006619719</v>
+        <v>129.013908673937</v>
       </c>
       <c r="O8" t="n">
-        <v>11.41261147424076</v>
+        <v>11.35842897032582</v>
       </c>
       <c r="P8" t="n">
-        <v>386.4830178119901</v>
+        <v>386.4344917007219</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25145,28 +25387,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2564730564844505</v>
+        <v>-0.2518184620321657</v>
       </c>
       <c r="J9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0335255023673473</v>
+        <v>0.03297593618814498</v>
       </c>
       <c r="M9" t="n">
-        <v>8.956611611087263</v>
+        <v>8.887089315491178</v>
       </c>
       <c r="N9" t="n">
-        <v>116.4984370053967</v>
+        <v>115.3983402754923</v>
       </c>
       <c r="O9" t="n">
-        <v>10.79344416789176</v>
+        <v>10.74236195049731</v>
       </c>
       <c r="P9" t="n">
-        <v>395.4893502015763</v>
+        <v>395.4440640194411</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25223,28 +25465,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2166699926137516</v>
+        <v>-0.21647895351146</v>
       </c>
       <c r="J10" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K10" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02803351085166461</v>
+        <v>0.02853761172194935</v>
       </c>
       <c r="M10" t="n">
-        <v>7.930025625315953</v>
+        <v>7.859386694092924</v>
       </c>
       <c r="N10" t="n">
-        <v>99.99835066729847</v>
+        <v>98.99744968066469</v>
       </c>
       <c r="O10" t="n">
-        <v>9.999917533024883</v>
+        <v>9.949746211872174</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0689856923829</v>
+        <v>385.0671179239479</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25301,28 +25543,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2653287889007861</v>
+        <v>-0.2648157816090302</v>
       </c>
       <c r="J11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04784388179530552</v>
+        <v>0.04858511144581146</v>
       </c>
       <c r="M11" t="n">
-        <v>7.105197149117816</v>
+        <v>7.04584395366437</v>
       </c>
       <c r="N11" t="n">
-        <v>86.07400326564274</v>
+        <v>85.21945399755725</v>
       </c>
       <c r="O11" t="n">
-        <v>9.2776076261956</v>
+        <v>9.231438349334152</v>
       </c>
       <c r="P11" t="n">
-        <v>377.7920374337218</v>
+        <v>377.7870355014713</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25379,28 +25621,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2651690571011047</v>
+        <v>-0.2641051086092478</v>
       </c>
       <c r="J12" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04990225527990122</v>
+        <v>0.05046661959495014</v>
       </c>
       <c r="M12" t="n">
-        <v>7.040169899559136</v>
+        <v>6.982702077901493</v>
       </c>
       <c r="N12" t="n">
-        <v>83.25875172933274</v>
+        <v>82.4414354531189</v>
       </c>
       <c r="O12" t="n">
-        <v>9.124623374656773</v>
+        <v>9.079726617752261</v>
       </c>
       <c r="P12" t="n">
-        <v>370.7826794217937</v>
+        <v>370.7724294549999</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25457,28 +25699,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2584562603992993</v>
+        <v>-0.2605802221403377</v>
       </c>
       <c r="J13" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K13" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05098626755109481</v>
+        <v>0.05276303063690702</v>
       </c>
       <c r="M13" t="n">
-        <v>6.954894682230448</v>
+        <v>6.89548149366884</v>
       </c>
       <c r="N13" t="n">
-        <v>77.32670091231739</v>
+        <v>76.57689036773914</v>
       </c>
       <c r="O13" t="n">
-        <v>8.793560195524757</v>
+        <v>8.750822268092247</v>
       </c>
       <c r="P13" t="n">
-        <v>364.8875756979317</v>
+        <v>364.9080013336787</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25535,28 +25777,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1422232177872934</v>
+        <v>-0.1491630530996204</v>
       </c>
       <c r="J14" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K14" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0195803393911671</v>
+        <v>0.02186977546805469</v>
       </c>
       <c r="M14" t="n">
-        <v>6.455783235508922</v>
+        <v>6.432781034541557</v>
       </c>
       <c r="N14" t="n">
-        <v>62.98960573730788</v>
+        <v>62.51162700780887</v>
       </c>
       <c r="O14" t="n">
-        <v>7.93659912918045</v>
+        <v>7.906429472765116</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5003745449944</v>
+        <v>359.5671429085204</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25613,28 +25855,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1375633199139083</v>
+        <v>-0.147678010420007</v>
       </c>
       <c r="J15" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K15" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01767585282362583</v>
+        <v>0.02062108022798492</v>
       </c>
       <c r="M15" t="n">
-        <v>6.737427247668467</v>
+        <v>6.730636886963079</v>
       </c>
       <c r="N15" t="n">
-        <v>65.4057353794728</v>
+        <v>65.06642197483745</v>
       </c>
       <c r="O15" t="n">
-        <v>8.087381243608638</v>
+        <v>8.06637601248773</v>
       </c>
       <c r="P15" t="n">
-        <v>358.2065543026105</v>
+        <v>358.3038752385486</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25691,28 +25933,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1016052388079624</v>
+        <v>-0.1191591507686618</v>
       </c>
       <c r="J16" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K16" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01134938393852847</v>
+        <v>0.01558703757344293</v>
       </c>
       <c r="M16" t="n">
-        <v>6.266736249081787</v>
+        <v>6.300428354280341</v>
       </c>
       <c r="N16" t="n">
-        <v>55.92923102219226</v>
+        <v>56.33190783436317</v>
       </c>
       <c r="O16" t="n">
-        <v>7.478584827505285</v>
+        <v>7.505458535916588</v>
       </c>
       <c r="P16" t="n">
-        <v>357.6825982895556</v>
+        <v>357.8514937700463</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -25769,28 +26011,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1031902338590344</v>
+        <v>-0.1261169772221283</v>
       </c>
       <c r="J17" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K17" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01191497769160932</v>
+        <v>0.0175320870656851</v>
       </c>
       <c r="M17" t="n">
-        <v>6.065136406872294</v>
+        <v>6.135005719208544</v>
       </c>
       <c r="N17" t="n">
-        <v>54.9179565387069</v>
+        <v>55.99094307248929</v>
       </c>
       <c r="O17" t="n">
-        <v>7.410665053738895</v>
+        <v>7.482709607654789</v>
       </c>
       <c r="P17" t="n">
-        <v>352.4955678512134</v>
+        <v>352.7161723249902</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -25847,28 +26089,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.04103135710381659</v>
+        <v>-0.05717281184349495</v>
       </c>
       <c r="J18" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K18" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001973459163947089</v>
+        <v>0.003843045744699403</v>
       </c>
       <c r="M18" t="n">
-        <v>5.964824928652831</v>
+        <v>5.988354795896038</v>
       </c>
       <c r="N18" t="n">
-        <v>52.95193104056784</v>
+        <v>53.22519251636188</v>
       </c>
       <c r="O18" t="n">
-        <v>7.276807750694521</v>
+        <v>7.29555978087781</v>
       </c>
       <c r="P18" t="n">
-        <v>347.7309474546464</v>
+        <v>347.8862628935273</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25925,28 +26167,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02472895844824177</v>
+        <v>0.01033926916491133</v>
       </c>
       <c r="J19" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K19" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0005516712273108126</v>
+        <v>9.752719060052151e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>6.76153796541838</v>
+        <v>6.757336169680101</v>
       </c>
       <c r="N19" t="n">
-        <v>68.90135378975212</v>
+        <v>68.84898331184795</v>
       </c>
       <c r="O19" t="n">
-        <v>8.300683935059334</v>
+        <v>8.297528747274573</v>
       </c>
       <c r="P19" t="n">
-        <v>343.9211581456118</v>
+        <v>344.0596178476583</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26003,28 +26245,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>0.006241055044775185</v>
+        <v>-0.0165478678850651</v>
       </c>
       <c r="J20" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K20" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L20" t="n">
-        <v>2.618233989648555e-05</v>
+        <v>0.0001845430641862489</v>
       </c>
       <c r="M20" t="n">
-        <v>7.690936595191657</v>
+        <v>7.70624989340242</v>
       </c>
       <c r="N20" t="n">
-        <v>92.51929003928528</v>
+        <v>93.19489616910516</v>
       </c>
       <c r="O20" t="n">
-        <v>9.618694819947521</v>
+        <v>9.653750368074842</v>
       </c>
       <c r="P20" t="n">
-        <v>345.1266724118223</v>
+        <v>345.3459507690724</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26081,28 +26323,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01346554460552195</v>
+        <v>-0.005891527293067539</v>
       </c>
       <c r="J21" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K21" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0001253722512931654</v>
+        <v>2.417553765021729e-05</v>
       </c>
       <c r="M21" t="n">
-        <v>7.427656280897486</v>
+        <v>7.430163123564687</v>
       </c>
       <c r="N21" t="n">
-        <v>89.93485988767179</v>
+        <v>90.18931054463947</v>
       </c>
       <c r="O21" t="n">
-        <v>9.483399173696728</v>
+        <v>9.496805280968935</v>
       </c>
       <c r="P21" t="n">
-        <v>347.9209124010869</v>
+        <v>348.1071689854971</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26159,28 +26401,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.06812939134186574</v>
+        <v>-0.07189532272992313</v>
       </c>
       <c r="J22" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K22" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002569844720444525</v>
+        <v>0.002917780798718073</v>
       </c>
       <c r="M22" t="n">
-        <v>7.786123608201703</v>
+        <v>7.725686879967805</v>
       </c>
       <c r="N22" t="n">
-        <v>112.0419665113419</v>
+        <v>110.959758952589</v>
       </c>
       <c r="O22" t="n">
-        <v>10.58498778985322</v>
+        <v>10.53374382413912</v>
       </c>
       <c r="P22" t="n">
-        <v>354.0163680666139</v>
+        <v>354.0526044029997</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26237,28 +26479,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07856967274526187</v>
+        <v>-0.08805110910035183</v>
       </c>
       <c r="J23" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K23" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003133228023670109</v>
+        <v>0.004002328149240064</v>
       </c>
       <c r="M23" t="n">
-        <v>8.099882325449096</v>
+        <v>8.061743746912194</v>
       </c>
       <c r="N23" t="n">
-        <v>122.1493328885828</v>
+        <v>121.1996068976802</v>
       </c>
       <c r="O23" t="n">
-        <v>11.05211893206831</v>
+        <v>11.00906930206546</v>
       </c>
       <c r="P23" t="n">
-        <v>360.5113517395784</v>
+        <v>360.6025835013371</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -26315,28 +26557,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.07320156726493032</v>
+        <v>-0.0881923847375965</v>
       </c>
       <c r="J24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002459969035514376</v>
+        <v>0.00362020284282627</v>
       </c>
       <c r="M24" t="n">
-        <v>8.75394315222343</v>
+        <v>8.741009601705937</v>
       </c>
       <c r="N24" t="n">
-        <v>135.138017783561</v>
+        <v>134.4745501651176</v>
       </c>
       <c r="O24" t="n">
-        <v>11.62488786111767</v>
+        <v>11.59631623254202</v>
       </c>
       <c r="P24" t="n">
-        <v>358.8289355494891</v>
+        <v>358.9731793844464</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -26393,28 +26635,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.04369324142499616</v>
+        <v>-0.05928196646715145</v>
       </c>
       <c r="J25" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K25" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L25" t="n">
-        <v>0.000838629110738065</v>
+        <v>0.001565474231079</v>
       </c>
       <c r="M25" t="n">
-        <v>9.024535986919012</v>
+        <v>9.008691962587372</v>
       </c>
       <c r="N25" t="n">
-        <v>141.4589152551378</v>
+        <v>140.800692198704</v>
       </c>
       <c r="O25" t="n">
-        <v>11.89365020736434</v>
+        <v>11.86594674683415</v>
       </c>
       <c r="P25" t="n">
-        <v>353.3760384219618</v>
+        <v>353.5260245576507</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -26471,28 +26713,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03508735113008979</v>
+        <v>0.01650281044842525</v>
       </c>
       <c r="J26" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K26" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0003826315679402725</v>
+        <v>8.592097139237254e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>10.46281378772971</v>
+        <v>10.44343589057046</v>
       </c>
       <c r="N26" t="n">
-        <v>200.0277524046374</v>
+        <v>199.0972436749728</v>
       </c>
       <c r="O26" t="n">
-        <v>14.1431167853708</v>
+        <v>14.11018226937458</v>
       </c>
       <c r="P26" t="n">
-        <v>347.2489075844037</v>
+        <v>347.4277199748726</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -26549,28 +26791,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1886315441482783</v>
+        <v>0.1680999603814967</v>
       </c>
       <c r="J27" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K27" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008937601663117523</v>
+        <v>0.007215606907786665</v>
       </c>
       <c r="M27" t="n">
-        <v>11.65501125887426</v>
+        <v>11.63589429403214</v>
       </c>
       <c r="N27" t="n">
-        <v>245.3831498884983</v>
+        <v>244.2323665250376</v>
       </c>
       <c r="O27" t="n">
-        <v>15.66471033528862</v>
+        <v>15.62793545306089</v>
       </c>
       <c r="P27" t="n">
-        <v>343.1746718644636</v>
+        <v>343.372218946233</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -26627,28 +26869,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3116725743509688</v>
+        <v>0.2862935075418483</v>
       </c>
       <c r="J28" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K28" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02542804468285875</v>
+        <v>0.02178380053172291</v>
       </c>
       <c r="M28" t="n">
-        <v>11.68395354538597</v>
+        <v>11.68777527672265</v>
       </c>
       <c r="N28" t="n">
-        <v>231.5443634430613</v>
+        <v>231.2118653576938</v>
       </c>
       <c r="O28" t="n">
-        <v>15.21658185806068</v>
+        <v>15.2056524147336</v>
       </c>
       <c r="P28" t="n">
-        <v>342.1460501990122</v>
+        <v>342.3902456280123</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -26705,28 +26947,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2844806559511031</v>
+        <v>0.2591119777610072</v>
       </c>
       <c r="J29" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K29" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01918673538068405</v>
+        <v>0.0161637450125599</v>
       </c>
       <c r="M29" t="n">
-        <v>12.2849329285509</v>
+        <v>12.26963898100799</v>
       </c>
       <c r="N29" t="n">
-        <v>257.2923177213002</v>
+        <v>256.7093754690649</v>
       </c>
       <c r="O29" t="n">
-        <v>16.04033409007743</v>
+        <v>16.0221526477894</v>
       </c>
       <c r="P29" t="n">
-        <v>344.8455483532029</v>
+        <v>345.0896381784898</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -26783,28 +27025,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3403652119063129</v>
+        <v>0.3165866718476999</v>
       </c>
       <c r="J30" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K30" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02718704865825072</v>
+        <v>0.02391555729880357</v>
       </c>
       <c r="M30" t="n">
-        <v>12.29662518179479</v>
+        <v>12.26837020966262</v>
       </c>
       <c r="N30" t="n">
-        <v>257.8064050352955</v>
+        <v>256.9674173836926</v>
       </c>
       <c r="O30" t="n">
-        <v>16.05635092526616</v>
+        <v>16.03020328578813</v>
       </c>
       <c r="P30" t="n">
-        <v>348.7222453792931</v>
+        <v>348.9510397560305</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -26861,28 +27103,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2876736436976781</v>
+        <v>0.26396105364581</v>
       </c>
       <c r="J31" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K31" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01903815554963439</v>
+        <v>0.01629203436195692</v>
       </c>
       <c r="M31" t="n">
-        <v>12.31817960873703</v>
+        <v>12.28287576088911</v>
       </c>
       <c r="N31" t="n">
-        <v>265.193872971772</v>
+        <v>264.2752528949237</v>
       </c>
       <c r="O31" t="n">
-        <v>16.2847742683702</v>
+        <v>16.25654492488867</v>
       </c>
       <c r="P31" t="n">
-        <v>348.3625420850067</v>
+        <v>348.5906991567803</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -26939,28 +27181,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2880460756265271</v>
+        <v>0.260391007124673</v>
       </c>
       <c r="J32" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K32" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01829962824468812</v>
+        <v>0.01517539105753296</v>
       </c>
       <c r="M32" t="n">
-        <v>12.64249840358365</v>
+        <v>12.61541425096228</v>
       </c>
       <c r="N32" t="n">
-        <v>276.8195171502338</v>
+        <v>276.4119937384658</v>
       </c>
       <c r="O32" t="n">
-        <v>16.63789401187043</v>
+        <v>16.62564265640477</v>
       </c>
       <c r="P32" t="n">
-        <v>347.7122695753756</v>
+        <v>347.978360807229</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -27017,28 +27259,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2831525626485371</v>
+        <v>0.2559962979542771</v>
       </c>
       <c r="J33" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K33" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01778523003997035</v>
+        <v>0.01475484654132975</v>
       </c>
       <c r="M33" t="n">
-        <v>12.51519979614111</v>
+        <v>12.49793412375591</v>
       </c>
       <c r="N33" t="n">
-        <v>275.3747143998716</v>
+        <v>274.8925056204357</v>
       </c>
       <c r="O33" t="n">
-        <v>16.59441816997124</v>
+        <v>16.57988255749828</v>
       </c>
       <c r="P33" t="n">
-        <v>350.4512389911559</v>
+        <v>350.712533283907</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -27095,28 +27337,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2243599879549384</v>
+        <v>0.196687462776865</v>
       </c>
       <c r="J34" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K34" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01064186961617131</v>
+        <v>0.008296195926131289</v>
       </c>
       <c r="M34" t="n">
-        <v>13.25623810269711</v>
+        <v>13.22856730523589</v>
       </c>
       <c r="N34" t="n">
-        <v>291.0465814227833</v>
+        <v>290.4974036296161</v>
       </c>
       <c r="O34" t="n">
-        <v>17.06008738027984</v>
+        <v>17.04398438246222</v>
       </c>
       <c r="P34" t="n">
-        <v>355.8852125104769</v>
+        <v>356.1514725541847</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -27154,7 +27396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI198"/>
+  <dimension ref="A1:AI200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62127,6 +62369,360 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-34.42626650701678,172.96361750555963</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>-34.426170828141046,172.96451402559092</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-34.42609291286001,172.9654109006193</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-34.42599615196048,172.966307396778</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-34.42589172658366,172.96720373800406</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-34.425750331333845,172.96809933598956</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-34.42561321708307,172.9689853050555</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-34.42542412987361,172.9697931492333</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-34.425224936784936,172.970625905133</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-34.42498761806306,172.97148195301807</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-34.424735207963195,172.97232967178311</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>-34.424488045110756,172.973180288407</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-34.424218328100366,172.97401845596266</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-34.42393133878522,172.97484809357582</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>-34.42364927191716,172.9756906162575</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>-34.423333023150384,172.97651679155095</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>-34.422958709540545,172.97729211876828</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>-34.422598390647764,172.97807715196257</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>-34.422260901989134,172.97887801855202</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>-34.421853586738706,172.97963046329326</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>-34.421385281040344,172.98034061301976</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>-34.420989963813724,172.98111011761156</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>-34.42057537108352,172.9818682318256</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>-34.42013197679302,172.98259826537185</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>-34.41968893454359,172.98332093568374</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>-34.41921434255498,172.98401093056256</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>-34.418732083491825,172.98469298694374</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>-34.41824010452507,172.98536497846413</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>-34.41770552575853,172.98600775343405</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>-34.417175508921325,172.9866533905541</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>-34.416651334567305,172.98729123057697</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>-34.41609049519707,172.98787949426713</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>-34.41552799134029,172.98846560988048</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>-34.42625045667023,172.9636171839855</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>-34.42614693296391,172.96451354667883</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-34.426075149276855,172.96541054447567</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-34.42597802769676,172.96630703327855</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-34.42587973391252,172.9672034973972</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-34.425728870765795,172.96809890528309</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-34.42559918989383,172.96898400436248</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-34.4254062135944,172.96978682121934</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-34.42520943675368,172.97061734915223</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-34.42496834558584,172.97147131452954</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-34.424714623368274,172.9723183088692</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-34.424469182779966,172.9731698760793</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-34.424205534550694,172.9740113936266</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-34.42392463010572,172.97484433905979</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>-34.42363183842394,172.97567964968252</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>-34.423333023150384,172.97651679155095</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>-34.422958709540545,172.97729211876828</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>-34.422598390647764,172.97807715196257</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>-34.422260901989134,172.97887801855202</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>-34.421853586738706,172.97963046329326</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>-34.421385281040344,172.98034061301976</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>-34.420989963813724,172.98111011761156</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>-34.42057537108352,172.9818682318256</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>-34.42011699030113,172.98258274278203</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>-34.41967401654297,172.98330548396913</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>-34.419199424609985,172.98399547885535</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>-34.418724213962726,172.9846848358185</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>-34.418224433953,172.985348747109</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>-34.41769727977672,172.98599831949014</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>-34.41716430293529,172.98663906873273</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>-34.41663902976971,172.9872753176758</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>-34.41608138968204,172.98786771875808</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>-34.41551673253687,172.98845104967089</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI200"/>
+  <dimension ref="A1:AI201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22659,6 +22659,117 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>317.88</v>
+      </c>
+      <c r="C201" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="D201" t="n">
+        <v>334.45</v>
+      </c>
+      <c r="E201" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="F201" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="G201" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="H201" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="I201" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="J201" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="K201" t="n">
+        <v>375.46</v>
+      </c>
+      <c r="L201" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="M201" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="N201" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="O201" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="P201" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="R201" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="S201" t="n">
+        <v>340.44</v>
+      </c>
+      <c r="T201" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="U201" t="n">
+        <v>340.14</v>
+      </c>
+      <c r="V201" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="W201" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="X201" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>346.47</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>342.06</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>339.17</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>343.77</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>344.69</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22670,7 +22781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24673,6 +24784,16 @@
       </c>
       <c r="B200" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -24841,28 +24962,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1906718688548203</v>
+        <v>-0.1935937695253067</v>
       </c>
       <c r="J2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004840349682717626</v>
+        <v>0.005040188756972097</v>
       </c>
       <c r="M2" t="n">
-        <v>17.49438292595818</v>
+        <v>17.42330703961559</v>
       </c>
       <c r="N2" t="n">
-        <v>452.4810954389674</v>
+        <v>450.2224448379495</v>
       </c>
       <c r="O2" t="n">
-        <v>21.27160302936682</v>
+        <v>21.21844586292666</v>
       </c>
       <c r="P2" t="n">
-        <v>326.102443349021</v>
+        <v>326.1317512903607</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24919,28 +25040,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1798135043839136</v>
+        <v>-0.1743911365750771</v>
       </c>
       <c r="J3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005662570203022188</v>
+        <v>0.005380191400500389</v>
       </c>
       <c r="M3" t="n">
-        <v>15.12656031319516</v>
+        <v>15.07171305894384</v>
       </c>
       <c r="N3" t="n">
-        <v>348.1279656249862</v>
+        <v>346.5357557217757</v>
       </c>
       <c r="O3" t="n">
-        <v>18.65818762969722</v>
+        <v>18.61547087026744</v>
       </c>
       <c r="P3" t="n">
-        <v>328.6782496553827</v>
+        <v>328.624447109769</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24997,28 +25118,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2934031031612657</v>
+        <v>-0.286469658508651</v>
       </c>
       <c r="J4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01860677108023967</v>
+        <v>0.01791563809005903</v>
       </c>
       <c r="M4" t="n">
-        <v>14.0770230773347</v>
+        <v>14.03172047771448</v>
       </c>
       <c r="N4" t="n">
-        <v>278.4040584189336</v>
+        <v>277.2768636389355</v>
       </c>
       <c r="O4" t="n">
-        <v>16.68544450768195</v>
+        <v>16.65163246168181</v>
       </c>
       <c r="P4" t="n">
-        <v>334.6888095875497</v>
+        <v>334.6200136324737</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25075,28 +25196,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3266904554531804</v>
+        <v>-0.317652479361185</v>
       </c>
       <c r="J5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K5" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02999873262210206</v>
+        <v>0.0286280886357001</v>
       </c>
       <c r="M5" t="n">
-        <v>12.32093210746876</v>
+        <v>12.29080940111403</v>
       </c>
       <c r="N5" t="n">
-        <v>214.6616127876568</v>
+        <v>214.0732077675892</v>
       </c>
       <c r="O5" t="n">
-        <v>14.65133484661574</v>
+        <v>14.63124081435301</v>
       </c>
       <c r="P5" t="n">
-        <v>343.8447768232382</v>
+        <v>343.7561735475659</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25153,28 +25274,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4013939035875331</v>
+        <v>-0.3949443438336002</v>
       </c>
       <c r="J6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K6" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04954345119786163</v>
+        <v>0.04845008566080755</v>
       </c>
       <c r="M6" t="n">
-        <v>11.39357363672015</v>
+        <v>11.35973224536729</v>
       </c>
       <c r="N6" t="n">
-        <v>192.2647448683586</v>
+        <v>191.5461609948428</v>
       </c>
       <c r="O6" t="n">
-        <v>13.8659563272195</v>
+        <v>13.84002026713989</v>
       </c>
       <c r="P6" t="n">
-        <v>356.3820429387378</v>
+        <v>356.3188150528675</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25231,28 +25352,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3658695224294126</v>
+        <v>-0.3571103863926163</v>
       </c>
       <c r="J7" t="n">
+        <v>200</v>
+      </c>
+      <c r="K7" t="n">
         <v>199</v>
       </c>
-      <c r="K7" t="n">
-        <v>198</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05089158191267296</v>
+        <v>0.04893211141154608</v>
       </c>
       <c r="M7" t="n">
-        <v>10.11648260897359</v>
+        <v>10.09536680841928</v>
       </c>
       <c r="N7" t="n">
-        <v>154.919691188377</v>
+        <v>154.6093616315782</v>
       </c>
       <c r="O7" t="n">
-        <v>12.44667390062008</v>
+        <v>12.43420128643485</v>
       </c>
       <c r="P7" t="n">
-        <v>369.3426426498118</v>
+        <v>369.2565286039013</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25309,28 +25430,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3406599105237517</v>
+        <v>-0.3363622293750885</v>
       </c>
       <c r="J8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K8" t="n">
         <v>199</v>
       </c>
-      <c r="K8" t="n">
-        <v>198</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.05286885696276378</v>
+        <v>0.05206847790394642</v>
       </c>
       <c r="M8" t="n">
-        <v>9.185250790370672</v>
+        <v>9.155201074653391</v>
       </c>
       <c r="N8" t="n">
-        <v>129.013908673937</v>
+        <v>128.4783021123523</v>
       </c>
       <c r="O8" t="n">
-        <v>11.35842897032582</v>
+        <v>11.33482695555395</v>
       </c>
       <c r="P8" t="n">
-        <v>386.4344917007219</v>
+        <v>386.3922397354379</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25387,28 +25508,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2518184620321657</v>
+        <v>-0.2458893644463971</v>
       </c>
       <c r="J9" t="n">
+        <v>200</v>
+      </c>
+      <c r="K9" t="n">
         <v>199</v>
       </c>
-      <c r="K9" t="n">
-        <v>198</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03297593618814498</v>
+        <v>0.03174392919319036</v>
       </c>
       <c r="M9" t="n">
-        <v>8.887089315491178</v>
+        <v>8.868397622118874</v>
       </c>
       <c r="N9" t="n">
-        <v>115.3983402754923</v>
+        <v>115.0329604377899</v>
       </c>
       <c r="O9" t="n">
-        <v>10.74236195049731</v>
+        <v>10.72534197299974</v>
       </c>
       <c r="P9" t="n">
-        <v>395.4440640194411</v>
+        <v>395.3857730442166</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25465,28 +25586,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.21647895351146</v>
+        <v>-0.2128748060339192</v>
       </c>
       <c r="J10" t="n">
+        <v>200</v>
+      </c>
+      <c r="K10" t="n">
         <v>199</v>
       </c>
-      <c r="K10" t="n">
-        <v>198</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02853761172194935</v>
+        <v>0.02787397450216267</v>
       </c>
       <c r="M10" t="n">
-        <v>7.859386694092924</v>
+        <v>7.83766489749132</v>
       </c>
       <c r="N10" t="n">
-        <v>98.99744968066469</v>
+        <v>98.57923944965664</v>
       </c>
       <c r="O10" t="n">
-        <v>9.949746211872174</v>
+        <v>9.92870784390681</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0671179239479</v>
+        <v>385.0316843240991</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25543,28 +25664,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2648157816090302</v>
+        <v>-0.2605712376348671</v>
       </c>
       <c r="J11" t="n">
+        <v>200</v>
+      </c>
+      <c r="K11" t="n">
         <v>199</v>
       </c>
-      <c r="K11" t="n">
-        <v>198</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.04858511144581146</v>
+        <v>0.04751292102072757</v>
       </c>
       <c r="M11" t="n">
-        <v>7.04584395366437</v>
+        <v>7.037729624765293</v>
       </c>
       <c r="N11" t="n">
-        <v>85.21945399755725</v>
+        <v>84.90115031031272</v>
       </c>
       <c r="O11" t="n">
-        <v>9.231438349334152</v>
+        <v>9.214182020684891</v>
       </c>
       <c r="P11" t="n">
-        <v>377.7870355014713</v>
+        <v>377.7453059458251</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25621,28 +25742,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2641051086092478</v>
+        <v>-0.2593097656157913</v>
       </c>
       <c r="J12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05046661959495014</v>
+        <v>0.04912964248623553</v>
       </c>
       <c r="M12" t="n">
-        <v>6.982702077901493</v>
+        <v>6.977072294097061</v>
       </c>
       <c r="N12" t="n">
-        <v>82.4414354531189</v>
+        <v>82.17185802494579</v>
       </c>
       <c r="O12" t="n">
-        <v>9.079726617752261</v>
+        <v>9.064869443348083</v>
       </c>
       <c r="P12" t="n">
-        <v>370.7724294549999</v>
+        <v>370.7257886852647</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25699,28 +25820,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2605802221403377</v>
+        <v>-0.2561330444451365</v>
       </c>
       <c r="J13" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K13" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05276303063690702</v>
+        <v>0.05148307928026541</v>
       </c>
       <c r="M13" t="n">
-        <v>6.89548149366884</v>
+        <v>6.88875143675142</v>
       </c>
       <c r="N13" t="n">
-        <v>76.57689036773914</v>
+        <v>76.3166763018417</v>
       </c>
       <c r="O13" t="n">
-        <v>8.750822268092247</v>
+        <v>8.735941637959911</v>
       </c>
       <c r="P13" t="n">
-        <v>364.9080013336787</v>
+        <v>364.8647469113911</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25777,28 +25898,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1491630530996204</v>
+        <v>-0.1484064422548159</v>
       </c>
       <c r="J14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02186977546805469</v>
+        <v>0.02186764990677081</v>
       </c>
       <c r="M14" t="n">
-        <v>6.432781034541557</v>
+        <v>6.404521061743205</v>
       </c>
       <c r="N14" t="n">
-        <v>62.51162700780887</v>
+        <v>62.20261958838285</v>
       </c>
       <c r="O14" t="n">
-        <v>7.906429472765116</v>
+        <v>7.886863735882778</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5671429085204</v>
+        <v>359.5597839120441</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25855,28 +25976,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.147678010420007</v>
+        <v>-0.15073562954791</v>
       </c>
       <c r="J15" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K15" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02062108022798492</v>
+        <v>0.02166009895006049</v>
       </c>
       <c r="M15" t="n">
-        <v>6.730636886963079</v>
+        <v>6.714982191351917</v>
       </c>
       <c r="N15" t="n">
-        <v>65.06642197483745</v>
+        <v>64.79907778603919</v>
       </c>
       <c r="O15" t="n">
-        <v>8.06637601248773</v>
+        <v>8.049787437320267</v>
       </c>
       <c r="P15" t="n">
-        <v>358.3038752385486</v>
+        <v>358.3336144480016</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -25933,28 +26054,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1191591507686618</v>
+        <v>-0.1243746291533564</v>
       </c>
       <c r="J16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01558703757344293</v>
+        <v>0.01707685794935865</v>
       </c>
       <c r="M16" t="n">
-        <v>6.300428354280341</v>
+        <v>6.298256792997932</v>
       </c>
       <c r="N16" t="n">
-        <v>56.33190783436317</v>
+        <v>56.21896538109722</v>
       </c>
       <c r="O16" t="n">
-        <v>7.505458535916588</v>
+        <v>7.497930739950672</v>
       </c>
       <c r="P16" t="n">
-        <v>357.8514937700463</v>
+        <v>357.9022208873205</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26011,28 +26132,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1261169772221283</v>
+        <v>-0.1343187311456233</v>
       </c>
       <c r="J17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0175320870656851</v>
+        <v>0.01989177463321812</v>
       </c>
       <c r="M17" t="n">
-        <v>6.135005719208544</v>
+        <v>6.152199193691255</v>
       </c>
       <c r="N17" t="n">
-        <v>55.99094307248929</v>
+        <v>56.12822672324871</v>
       </c>
       <c r="O17" t="n">
-        <v>7.482709607654789</v>
+        <v>7.491877383089549</v>
       </c>
       <c r="P17" t="n">
-        <v>352.7161723249902</v>
+        <v>352.795944745168</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26089,28 +26210,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05717281184349495</v>
+        <v>-0.06341419663517811</v>
       </c>
       <c r="J18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003843045744699403</v>
+        <v>0.004750021632665802</v>
       </c>
       <c r="M18" t="n">
-        <v>5.988354795896038</v>
+        <v>5.990046088126901</v>
       </c>
       <c r="N18" t="n">
-        <v>53.22519251636188</v>
+        <v>53.20068644403234</v>
       </c>
       <c r="O18" t="n">
-        <v>7.29555978087781</v>
+        <v>7.29388006783991</v>
       </c>
       <c r="P18" t="n">
-        <v>347.8862628935273</v>
+        <v>347.9469682468867</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26167,28 +26288,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01033926916491133</v>
+        <v>0.006865991915801423</v>
       </c>
       <c r="J19" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K19" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="n">
-        <v>9.752719060052151e-05</v>
+        <v>4.340109271072645e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>6.757336169680101</v>
+        <v>6.738531783711916</v>
       </c>
       <c r="N19" t="n">
-        <v>68.84898331184795</v>
+        <v>68.57956390245441</v>
       </c>
       <c r="O19" t="n">
-        <v>8.297528747274573</v>
+        <v>8.281277914818123</v>
       </c>
       <c r="P19" t="n">
-        <v>344.0596178476583</v>
+        <v>344.0933998575423</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26245,28 +26366,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0165478678850651</v>
+        <v>-0.02253372832149671</v>
       </c>
       <c r="J20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0001845430641862489</v>
+        <v>0.0003448015166495066</v>
       </c>
       <c r="M20" t="n">
-        <v>7.70624989340242</v>
+        <v>7.691750673053303</v>
       </c>
       <c r="N20" t="n">
-        <v>93.19489616910516</v>
+        <v>92.95116256392795</v>
       </c>
       <c r="O20" t="n">
-        <v>9.653750368074842</v>
+        <v>9.641118325377402</v>
       </c>
       <c r="P20" t="n">
-        <v>345.3459507690724</v>
+        <v>345.4041708252108</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26323,28 +26444,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.005891527293067539</v>
+        <v>-0.01285124146684561</v>
       </c>
       <c r="J21" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>2.417553765021729e-05</v>
+        <v>0.0001158024707345051</v>
       </c>
       <c r="M21" t="n">
-        <v>7.430163123564687</v>
+        <v>7.420689644135479</v>
       </c>
       <c r="N21" t="n">
-        <v>90.18931054463947</v>
+        <v>90.03880110082083</v>
       </c>
       <c r="O21" t="n">
-        <v>9.496805280968935</v>
+        <v>9.488877757713018</v>
       </c>
       <c r="P21" t="n">
-        <v>348.1071689854971</v>
+        <v>348.1748609997376</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26401,28 +26522,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07189532272992313</v>
+        <v>-0.07472676360552694</v>
       </c>
       <c r="J22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002917780798718073</v>
+        <v>0.003181938308521093</v>
       </c>
       <c r="M22" t="n">
-        <v>7.725686879967805</v>
+        <v>7.700118103919599</v>
       </c>
       <c r="N22" t="n">
-        <v>110.959758952589</v>
+        <v>110.4546864137434</v>
       </c>
       <c r="O22" t="n">
-        <v>10.53374382413912</v>
+        <v>10.50974245230317</v>
       </c>
       <c r="P22" t="n">
-        <v>354.0526044029997</v>
+        <v>354.0801437431633</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26479,28 +26600,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08805110910035183</v>
+        <v>-0.09342245295268298</v>
       </c>
       <c r="J23" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K23" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004002328149240064</v>
+        <v>0.004542184536489913</v>
       </c>
       <c r="M23" t="n">
-        <v>8.061743746912194</v>
+        <v>8.045281409190101</v>
       </c>
       <c r="N23" t="n">
-        <v>121.1996068976802</v>
+        <v>120.7725609124927</v>
       </c>
       <c r="O23" t="n">
-        <v>11.00906930206546</v>
+        <v>10.98965699703556</v>
       </c>
       <c r="P23" t="n">
-        <v>360.6025835013371</v>
+        <v>360.6548266072269</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -26557,28 +26678,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0881923847375965</v>
+        <v>-0.09421436358804824</v>
       </c>
       <c r="J24" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K24" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00362020284282627</v>
+        <v>0.004164251579676148</v>
       </c>
       <c r="M24" t="n">
-        <v>8.741009601705937</v>
+        <v>8.726648474174903</v>
       </c>
       <c r="N24" t="n">
-        <v>134.4745501651176</v>
+        <v>134.0271083644411</v>
       </c>
       <c r="O24" t="n">
-        <v>11.59631623254202</v>
+        <v>11.57700774658293</v>
       </c>
       <c r="P24" t="n">
-        <v>358.9731793844464</v>
+        <v>359.0317507377985</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -26635,28 +26756,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.05928196646715145</v>
+        <v>-0.06416732361126011</v>
       </c>
       <c r="J25" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K25" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001565474231079</v>
+        <v>0.001850310670681976</v>
       </c>
       <c r="M25" t="n">
-        <v>9.008691962587372</v>
+        <v>8.986529148418883</v>
       </c>
       <c r="N25" t="n">
-        <v>140.800692198704</v>
+        <v>140.2447233950007</v>
       </c>
       <c r="O25" t="n">
-        <v>11.86594674683415</v>
+        <v>11.8424965017939</v>
       </c>
       <c r="P25" t="n">
-        <v>353.5260245576507</v>
+        <v>353.5735408287377</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -26713,28 +26834,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01650281044842525</v>
+        <v>0.01132496694379317</v>
       </c>
       <c r="J26" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L26" t="n">
-        <v>8.592097139237254e-05</v>
+        <v>4.084238295354314e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>10.44343589057046</v>
+        <v>10.41447687463988</v>
       </c>
       <c r="N26" t="n">
-        <v>199.0972436749728</v>
+        <v>198.2680484034976</v>
       </c>
       <c r="O26" t="n">
-        <v>14.11018226937458</v>
+        <v>14.08076874334273</v>
       </c>
       <c r="P26" t="n">
-        <v>347.4277199748726</v>
+        <v>347.4780810453848</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -26791,28 +26912,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1680999603814967</v>
+        <v>0.1637421205507525</v>
       </c>
       <c r="J27" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L27" t="n">
-        <v>0.007215606907786665</v>
+        <v>0.006914777978546227</v>
       </c>
       <c r="M27" t="n">
-        <v>11.63589429403214</v>
+        <v>11.59816652561221</v>
       </c>
       <c r="N27" t="n">
-        <v>244.2323665250376</v>
+        <v>243.1289960138746</v>
       </c>
       <c r="O27" t="n">
-        <v>15.62793545306089</v>
+        <v>15.59259426823755</v>
       </c>
       <c r="P27" t="n">
-        <v>343.372218946233</v>
+        <v>343.4146044449065</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -26869,28 +26990,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2862935075418483</v>
+        <v>0.2766445502852523</v>
       </c>
       <c r="J28" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02178380053172291</v>
+        <v>0.02052222793467429</v>
       </c>
       <c r="M28" t="n">
-        <v>11.68777527672265</v>
+        <v>11.67469597435192</v>
       </c>
       <c r="N28" t="n">
-        <v>231.2118653576938</v>
+        <v>230.6332788283346</v>
       </c>
       <c r="O28" t="n">
-        <v>15.2056524147336</v>
+        <v>15.18661512083369</v>
       </c>
       <c r="P28" t="n">
-        <v>342.3902456280123</v>
+        <v>342.4840939292085</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -26947,28 +27068,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2591119777610072</v>
+        <v>0.2490764936266932</v>
       </c>
       <c r="J29" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K29" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0161637450125599</v>
+        <v>0.01506793717782728</v>
       </c>
       <c r="M29" t="n">
-        <v>12.26963898100799</v>
+        <v>12.25016848008538</v>
       </c>
       <c r="N29" t="n">
-        <v>256.7093754690649</v>
+        <v>256.0504939516197</v>
       </c>
       <c r="O29" t="n">
-        <v>16.0221526477894</v>
+        <v>16.00157785818698</v>
       </c>
       <c r="P29" t="n">
-        <v>345.0896381784898</v>
+        <v>345.1872459419653</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27025,28 +27146,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3165866718476999</v>
+        <v>0.3044702109741376</v>
       </c>
       <c r="J30" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02391555729880357</v>
+        <v>0.02230265760527073</v>
       </c>
       <c r="M30" t="n">
-        <v>12.26837020966262</v>
+        <v>12.25592685820462</v>
       </c>
       <c r="N30" t="n">
-        <v>256.9674173836926</v>
+        <v>256.5931691599302</v>
       </c>
       <c r="O30" t="n">
-        <v>16.03020328578813</v>
+        <v>16.01852581107045</v>
       </c>
       <c r="P30" t="n">
-        <v>348.9510397560305</v>
+        <v>349.0688876476996</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -27103,28 +27224,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.26396105364581</v>
+        <v>0.2542285351541154</v>
       </c>
       <c r="J31" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K31" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01629203436195692</v>
+        <v>0.0152487397456853</v>
       </c>
       <c r="M31" t="n">
-        <v>12.28287576088911</v>
+        <v>12.25673772884167</v>
       </c>
       <c r="N31" t="n">
-        <v>264.2752528949237</v>
+        <v>263.541394717407</v>
       </c>
       <c r="O31" t="n">
-        <v>16.25654492488867</v>
+        <v>16.23395807304574</v>
       </c>
       <c r="P31" t="n">
-        <v>348.5906991567803</v>
+        <v>348.6853601965711</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -27181,28 +27302,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.260391007124673</v>
+        <v>0.2498489975227309</v>
       </c>
       <c r="J32" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K32" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01517539105753296</v>
+        <v>0.01409390515340925</v>
       </c>
       <c r="M32" t="n">
-        <v>12.61541425096228</v>
+        <v>12.58972574319993</v>
       </c>
       <c r="N32" t="n">
-        <v>276.4119937384658</v>
+        <v>275.7192485343888</v>
       </c>
       <c r="O32" t="n">
-        <v>16.62564265640477</v>
+        <v>16.60479594979682</v>
       </c>
       <c r="P32" t="n">
-        <v>347.978360807229</v>
+        <v>348.0808951708941</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -27259,28 +27380,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2559962979542771</v>
+        <v>0.2462039048361003</v>
       </c>
       <c r="J33" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K33" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01475484654132975</v>
+        <v>0.01377038974354583</v>
       </c>
       <c r="M33" t="n">
-        <v>12.49793412375591</v>
+        <v>12.4739084816488</v>
       </c>
       <c r="N33" t="n">
-        <v>274.8925056204357</v>
+        <v>274.112812258673</v>
       </c>
       <c r="O33" t="n">
-        <v>16.57988255749828</v>
+        <v>16.55635262546292</v>
       </c>
       <c r="P33" t="n">
-        <v>350.712533283907</v>
+        <v>350.8077766800945</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -27337,28 +27458,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.196687462776865</v>
+        <v>0.1847242425167134</v>
       </c>
       <c r="J34" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K34" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L34" t="n">
-        <v>0.008296195926131289</v>
+        <v>0.007376374804096142</v>
       </c>
       <c r="M34" t="n">
-        <v>13.22856730523589</v>
+        <v>13.20704766912633</v>
       </c>
       <c r="N34" t="n">
-        <v>290.4974036296161</v>
+        <v>289.9326181315621</v>
       </c>
       <c r="O34" t="n">
-        <v>17.04398438246222</v>
+        <v>17.02740785121335</v>
       </c>
       <c r="P34" t="n">
-        <v>356.1514725541847</v>
+        <v>356.2678299872622</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -27396,7 +27517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI200"/>
+  <dimension ref="A1:AI201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62723,6 +62844,183 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>-34.42624189047402,172.9636170123589</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>-34.42612186557044,172.96451304427322</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-34.42606757495711,172.9654103926175</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-34.42595873121691,172.96630664626937</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-34.42587693862826,172.96720344131595</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-34.42571561570902,172.96809863925856</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-34.42558812999457,172.96898297881637</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-34.425380421075836,172.96977771132958</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-34.42518557162496,172.97060417566422</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-34.424942020200454,172.9714567828148</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-34.42468600175831,172.97230250944835</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-34.42442858776052,172.97314746695508</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-34.424174124744226,172.97399405469537</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-34.423911049119994,172.97483673845593</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-34.42361088624264,172.97566646967636</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>-34.423307219745176,172.97649889794837</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>-34.42294463499523,172.97728235857969</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>-34.4225673485429,172.97805562523246</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>-34.42221609827478,172.97884694833493</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>-34.42183200594993,172.97961549747998</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>-34.42139419482257,172.9803467945653</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>-34.420996518057834,172.9811153219896</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>-34.42056545201629,172.98185863073104</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>-34.42010378302577,172.98256906306136</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>-34.41965170796953,172.98328237728683</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>-34.41916336149619,172.983958125439</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>-34.418706969427454,172.98466697422765</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>-34.41821410095451,172.985338044341</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>-34.41770493675985,172.98600707958084</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>-34.417156935462906,172.9866296527307</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>-34.416624694677886,172.98725677915183</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>-34.41606194817316,172.98784257646346</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>-34.41551168760798,172.98844452542522</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI201"/>
+  <dimension ref="A1:AI203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22770,6 +22770,228 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>318.43</v>
+      </c>
+      <c r="C202" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="D202" t="n">
+        <v>336.19</v>
+      </c>
+      <c r="E202" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="F202" t="n">
+        <v>353.16</v>
+      </c>
+      <c r="G202" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="H202" t="n">
+        <v>381.95</v>
+      </c>
+      <c r="I202" t="n">
+        <v>395.01</v>
+      </c>
+      <c r="J202" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="K202" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="L202" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="M202" t="n">
+        <v>362.28</v>
+      </c>
+      <c r="N202" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="O202" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="P202" t="n">
+        <v>349.2</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="R202" t="n">
+        <v>339.26</v>
+      </c>
+      <c r="S202" t="n">
+        <v>339.91</v>
+      </c>
+      <c r="T202" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="U202" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="V202" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="W202" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="X202" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>344.07</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>342.53</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="C203" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>338.13</v>
+      </c>
+      <c r="E203" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="F203" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="G203" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="H203" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="I203" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="J203" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="K203" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="L203" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="M203" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="N203" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="O203" t="n">
+        <v>354.46</v>
+      </c>
+      <c r="P203" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="R203" t="n">
+        <v>341.61</v>
+      </c>
+      <c r="S203" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="T203" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="U203" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="V203" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="W203" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="X203" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>345.79</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>342.03</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>342.58</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>344.13</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>345.51</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22781,7 +23003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24794,6 +25016,26 @@
       </c>
       <c r="B201" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -24962,28 +25204,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1935937695253067</v>
+        <v>-0.1909341003835472</v>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K2" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005040188756972097</v>
+        <v>0.005001233195449317</v>
       </c>
       <c r="M2" t="n">
-        <v>17.42330703961559</v>
+        <v>17.28592745165724</v>
       </c>
       <c r="N2" t="n">
-        <v>450.2224448379495</v>
+        <v>445.8580181868986</v>
       </c>
       <c r="O2" t="n">
-        <v>21.21844586292666</v>
+        <v>21.11535029751812</v>
       </c>
       <c r="P2" t="n">
-        <v>326.1317512903607</v>
+        <v>326.1048804913867</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25040,28 +25282,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1743911365750771</v>
+        <v>-0.1549860122205227</v>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005380191400500389</v>
+        <v>0.00432490911610206</v>
       </c>
       <c r="M3" t="n">
-        <v>15.07171305894384</v>
+        <v>14.99738635636374</v>
       </c>
       <c r="N3" t="n">
-        <v>346.5357557217757</v>
+        <v>344.3084742424248</v>
       </c>
       <c r="O3" t="n">
-        <v>18.61547087026744</v>
+        <v>18.55555103580664</v>
       </c>
       <c r="P3" t="n">
-        <v>328.624447109769</v>
+        <v>328.4312790355247</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25118,28 +25360,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.286469658508651</v>
+        <v>-0.2682810336673622</v>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01791563809005903</v>
+        <v>0.01600511749631095</v>
       </c>
       <c r="M4" t="n">
-        <v>14.03172047771448</v>
+        <v>13.9592030319116</v>
       </c>
       <c r="N4" t="n">
-        <v>277.2768636389355</v>
+        <v>275.5091088384936</v>
       </c>
       <c r="O4" t="n">
-        <v>16.65163246168181</v>
+        <v>16.59846706290956</v>
       </c>
       <c r="P4" t="n">
-        <v>334.6200136324737</v>
+        <v>334.4390176249785</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25196,28 +25438,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.317652479361185</v>
+        <v>-0.2975087553539028</v>
       </c>
       <c r="J5" t="n">
+        <v>202</v>
+      </c>
+      <c r="K5" t="n">
         <v>200</v>
       </c>
-      <c r="K5" t="n">
-        <v>198</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0286280886357001</v>
+        <v>0.02554895120994716</v>
       </c>
       <c r="M5" t="n">
-        <v>12.29080940111403</v>
+        <v>12.23822625684711</v>
       </c>
       <c r="N5" t="n">
-        <v>214.0732077675892</v>
+        <v>213.2103546961586</v>
       </c>
       <c r="O5" t="n">
-        <v>14.63124081435301</v>
+        <v>14.60172437406482</v>
       </c>
       <c r="P5" t="n">
-        <v>343.7561735475659</v>
+        <v>343.5581127684342</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25274,28 +25516,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3949443438336002</v>
+        <v>-0.3800893559768347</v>
       </c>
       <c r="J6" t="n">
+        <v>202</v>
+      </c>
+      <c r="K6" t="n">
         <v>200</v>
       </c>
-      <c r="K6" t="n">
-        <v>198</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04845008566080755</v>
+        <v>0.04574606353395072</v>
       </c>
       <c r="M6" t="n">
-        <v>11.35973224536729</v>
+        <v>11.29984202985637</v>
       </c>
       <c r="N6" t="n">
-        <v>191.5461609948428</v>
+        <v>190.3283519452802</v>
       </c>
       <c r="O6" t="n">
-        <v>13.84002026713989</v>
+        <v>13.79595418756094</v>
       </c>
       <c r="P6" t="n">
-        <v>356.3188150528675</v>
+        <v>356.1727510058079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25352,28 +25594,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3571103863926163</v>
+        <v>-0.3369868277604319</v>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04893211141154608</v>
+        <v>0.04429705191939004</v>
       </c>
       <c r="M7" t="n">
-        <v>10.09536680841928</v>
+        <v>10.06352960862645</v>
       </c>
       <c r="N7" t="n">
-        <v>154.6093616315782</v>
+        <v>154.3477410959965</v>
       </c>
       <c r="O7" t="n">
-        <v>12.43420128643485</v>
+        <v>12.42367663358945</v>
       </c>
       <c r="P7" t="n">
-        <v>369.2565286039013</v>
+        <v>369.0581100245476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25430,28 +25672,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3363622293750885</v>
+        <v>-0.3282443165540106</v>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K8" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05206847790394642</v>
+        <v>0.05058106341125801</v>
       </c>
       <c r="M8" t="n">
-        <v>9.155201074653391</v>
+        <v>9.094589534757111</v>
       </c>
       <c r="N8" t="n">
-        <v>128.4783021123523</v>
+        <v>127.4062372175084</v>
       </c>
       <c r="O8" t="n">
-        <v>11.33482695555395</v>
+        <v>11.28743714124284</v>
       </c>
       <c r="P8" t="n">
-        <v>386.3922397354379</v>
+        <v>386.3122056563066</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25508,28 +25750,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2458893644463971</v>
+        <v>-0.2347790344271724</v>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K9" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03174392919319036</v>
+        <v>0.02949129107207538</v>
       </c>
       <c r="M9" t="n">
-        <v>8.868397622118874</v>
+        <v>8.828036369040619</v>
       </c>
       <c r="N9" t="n">
-        <v>115.0329604377899</v>
+        <v>114.274834491694</v>
       </c>
       <c r="O9" t="n">
-        <v>10.72534197299974</v>
+        <v>10.68994080861508</v>
       </c>
       <c r="P9" t="n">
-        <v>395.3857730442166</v>
+        <v>395.2762368014957</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25586,28 +25828,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2128748060339192</v>
+        <v>-0.203913284374073</v>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02787397450216267</v>
+        <v>0.02606852887101696</v>
       </c>
       <c r="M10" t="n">
-        <v>7.83766489749132</v>
+        <v>7.803311852895753</v>
       </c>
       <c r="N10" t="n">
-        <v>98.57923944965664</v>
+        <v>97.86541478903686</v>
       </c>
       <c r="O10" t="n">
-        <v>9.92870784390681</v>
+        <v>9.892695021531638</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0316843240991</v>
+        <v>384.9432994180783</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25664,28 +25906,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2605712376348671</v>
+        <v>-0.2548678886129119</v>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K11" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04751292102072757</v>
+        <v>0.04636897291626241</v>
       </c>
       <c r="M11" t="n">
-        <v>7.037729624765293</v>
+        <v>7.00451089366637</v>
       </c>
       <c r="N11" t="n">
-        <v>84.90115031031272</v>
+        <v>84.16072421918295</v>
       </c>
       <c r="O11" t="n">
-        <v>9.214182020684891</v>
+        <v>9.173915424680072</v>
       </c>
       <c r="P11" t="n">
-        <v>377.7453059458251</v>
+        <v>377.6890640560437</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25742,28 +25984,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2593097656157913</v>
+        <v>-0.252286720084098</v>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04912964248623553</v>
+        <v>0.04742895817209591</v>
       </c>
       <c r="M12" t="n">
-        <v>6.977072294097061</v>
+        <v>6.950283036249037</v>
       </c>
       <c r="N12" t="n">
-        <v>82.17185802494579</v>
+        <v>81.51730955222072</v>
       </c>
       <c r="O12" t="n">
-        <v>9.064869443348083</v>
+        <v>9.028693679166478</v>
       </c>
       <c r="P12" t="n">
-        <v>370.7257886852647</v>
+        <v>370.6573030734154</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25820,28 +26062,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2561330444451365</v>
+        <v>-0.2480714090305479</v>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05148307928026541</v>
+        <v>0.04924218140556658</v>
       </c>
       <c r="M13" t="n">
-        <v>6.88875143675142</v>
+        <v>6.87009562372868</v>
       </c>
       <c r="N13" t="n">
-        <v>76.3166763018417</v>
+        <v>75.76930698949081</v>
       </c>
       <c r="O13" t="n">
-        <v>8.735941637959911</v>
+        <v>8.70455667966444</v>
       </c>
       <c r="P13" t="n">
-        <v>364.8647469113911</v>
+        <v>364.7861064533545</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25898,28 +26140,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1484064422548159</v>
+        <v>-0.1450941751337739</v>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K14" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02186764990677081</v>
+        <v>0.02131936179405369</v>
       </c>
       <c r="M14" t="n">
-        <v>6.404521061743205</v>
+        <v>6.357926691261999</v>
       </c>
       <c r="N14" t="n">
-        <v>62.20261958838285</v>
+        <v>61.62742458550377</v>
       </c>
       <c r="O14" t="n">
-        <v>7.886863735882778</v>
+        <v>7.850313661600011</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5597839120441</v>
+        <v>359.5274555719368</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -25976,28 +26218,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.15073562954791</v>
+        <v>-0.1533996465818853</v>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K15" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02166009895006049</v>
+        <v>0.02283665276355407</v>
       </c>
       <c r="M15" t="n">
-        <v>6.714982191351917</v>
+        <v>6.665875569365885</v>
       </c>
       <c r="N15" t="n">
-        <v>64.79907778603919</v>
+        <v>64.208230964854</v>
       </c>
       <c r="O15" t="n">
-        <v>8.049787437320267</v>
+        <v>8.013003866519346</v>
       </c>
       <c r="P15" t="n">
-        <v>358.3336144480016</v>
+        <v>358.3595488992343</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26054,28 +26296,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1243746291533564</v>
+        <v>-0.131351098623091</v>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K16" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01707685794935865</v>
+        <v>0.01932346780902905</v>
       </c>
       <c r="M16" t="n">
-        <v>6.298256792997932</v>
+        <v>6.274593663671562</v>
       </c>
       <c r="N16" t="n">
-        <v>56.21896538109722</v>
+        <v>55.83614163812072</v>
       </c>
       <c r="O16" t="n">
-        <v>7.497930739950672</v>
+        <v>7.472358505727675</v>
       </c>
       <c r="P16" t="n">
-        <v>357.9022208873205</v>
+        <v>357.9702255296162</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26132,28 +26374,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1343187311456233</v>
+        <v>-0.1493580158482989</v>
       </c>
       <c r="J17" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K17" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01989177463321812</v>
+        <v>0.02464164332352392</v>
       </c>
       <c r="M17" t="n">
-        <v>6.152199193691255</v>
+        <v>6.17868840104878</v>
       </c>
       <c r="N17" t="n">
-        <v>56.12822672324871</v>
+        <v>56.30654502099467</v>
       </c>
       <c r="O17" t="n">
-        <v>7.491877383089549</v>
+        <v>7.503768721182355</v>
       </c>
       <c r="P17" t="n">
-        <v>352.795944745168</v>
+        <v>352.9425948393275</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26210,28 +26452,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.06341419663517811</v>
+        <v>-0.07353335234923057</v>
       </c>
       <c r="J18" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K18" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004750021632665802</v>
+        <v>0.006462071626980093</v>
       </c>
       <c r="M18" t="n">
-        <v>5.990046088126901</v>
+        <v>5.98129115710902</v>
       </c>
       <c r="N18" t="n">
-        <v>53.20068644403234</v>
+        <v>53.01376898643215</v>
       </c>
       <c r="O18" t="n">
-        <v>7.29388006783991</v>
+        <v>7.281055485740523</v>
       </c>
       <c r="P18" t="n">
-        <v>347.9469682468867</v>
+        <v>348.0456305615149</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26288,28 +26530,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006865991915801423</v>
+        <v>-0.002166606685495277</v>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K19" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L19" t="n">
-        <v>4.340109271072645e-05</v>
+        <v>4.391311144824606e-06</v>
       </c>
       <c r="M19" t="n">
-        <v>6.738531783711916</v>
+        <v>6.710148083682878</v>
       </c>
       <c r="N19" t="n">
-        <v>68.57956390245441</v>
+        <v>68.16654887252552</v>
       </c>
       <c r="O19" t="n">
-        <v>8.281277914818123</v>
+        <v>8.256303584082016</v>
       </c>
       <c r="P19" t="n">
-        <v>344.0933998575423</v>
+        <v>344.1815226859302</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26366,28 +26608,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02253372832149671</v>
+        <v>-0.03442179149784106</v>
       </c>
       <c r="J20" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0003448015166495066</v>
+        <v>0.0008162968738345544</v>
       </c>
       <c r="M20" t="n">
-        <v>7.691750673053303</v>
+        <v>7.662722396755258</v>
       </c>
       <c r="N20" t="n">
-        <v>92.95116256392795</v>
+        <v>92.48502417024368</v>
       </c>
       <c r="O20" t="n">
-        <v>9.641118325377402</v>
+        <v>9.616913443004657</v>
       </c>
       <c r="P20" t="n">
-        <v>345.4041708252108</v>
+        <v>345.5201407969097</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26444,28 +26686,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.01285124146684561</v>
+        <v>-0.02656520695884692</v>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K21" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0001158024707345051</v>
+        <v>0.0005011529947943627</v>
       </c>
       <c r="M21" t="n">
-        <v>7.420689644135479</v>
+        <v>7.400845259937906</v>
       </c>
       <c r="N21" t="n">
-        <v>90.03880110082083</v>
+        <v>89.75231128445915</v>
       </c>
       <c r="O21" t="n">
-        <v>9.488877757713018</v>
+        <v>9.473769644891053</v>
       </c>
       <c r="P21" t="n">
-        <v>348.1748609997376</v>
+        <v>348.3086440050173</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26522,28 +26764,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07472676360552694</v>
+        <v>-0.08357515975812516</v>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K22" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003181938308521093</v>
+        <v>0.004046681729431123</v>
       </c>
       <c r="M22" t="n">
-        <v>7.700118103919599</v>
+        <v>7.664040448003522</v>
       </c>
       <c r="N22" t="n">
-        <v>110.4546864137434</v>
+        <v>109.6229870270119</v>
       </c>
       <c r="O22" t="n">
-        <v>10.50974245230317</v>
+        <v>10.47009966652715</v>
       </c>
       <c r="P22" t="n">
-        <v>354.0801437431633</v>
+        <v>354.1664795818755</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26600,28 +26842,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09342245295268298</v>
+        <v>-0.1037889606696822</v>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K23" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004542184536489913</v>
+        <v>0.005695638069562414</v>
       </c>
       <c r="M23" t="n">
-        <v>8.045281409190101</v>
+        <v>8.011274071501196</v>
       </c>
       <c r="N23" t="n">
-        <v>120.7725609124927</v>
+        <v>119.9186008862487</v>
       </c>
       <c r="O23" t="n">
-        <v>10.98965699703556</v>
+        <v>10.95073517560573</v>
       </c>
       <c r="P23" t="n">
-        <v>360.6548266072269</v>
+        <v>360.7559361613238</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -26678,28 +26920,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.09421436358804824</v>
+        <v>-0.1053823674881417</v>
       </c>
       <c r="J24" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K24" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004164251579676148</v>
+        <v>0.005292621210375659</v>
       </c>
       <c r="M24" t="n">
-        <v>8.726648474174903</v>
+        <v>8.695136183813684</v>
       </c>
       <c r="N24" t="n">
-        <v>134.0271083644411</v>
+        <v>133.0968248883595</v>
       </c>
       <c r="O24" t="n">
-        <v>11.57700774658293</v>
+        <v>11.53675972222528</v>
       </c>
       <c r="P24" t="n">
-        <v>359.0317507377985</v>
+        <v>359.140678702891</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -26756,28 +26998,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.06416732361126011</v>
+        <v>-0.07020124514714997</v>
       </c>
       <c r="J25" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K25" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001850310670681976</v>
+        <v>0.002256168315304063</v>
       </c>
       <c r="M25" t="n">
-        <v>8.986529148418883</v>
+        <v>8.926096754100444</v>
       </c>
       <c r="N25" t="n">
-        <v>140.2447233950007</v>
+        <v>138.9774863636616</v>
       </c>
       <c r="O25" t="n">
-        <v>11.8424965017939</v>
+        <v>11.78887129303148</v>
       </c>
       <c r="P25" t="n">
-        <v>353.5735408287377</v>
+        <v>353.6323708878659</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -26834,28 +27076,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01132496694379317</v>
+        <v>0.006149479320782433</v>
       </c>
       <c r="J26" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K26" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L26" t="n">
-        <v>4.084238295354314e-05</v>
+        <v>1.227854172158871e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>10.41447687463988</v>
+        <v>10.33426721771347</v>
       </c>
       <c r="N26" t="n">
-        <v>198.2680484034976</v>
+        <v>196.3956365009445</v>
       </c>
       <c r="O26" t="n">
-        <v>14.08076874334273</v>
+        <v>14.01412275174385</v>
       </c>
       <c r="P26" t="n">
-        <v>347.4780810453848</v>
+        <v>347.528538541528</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -26912,28 +27154,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1637421205507525</v>
+        <v>0.1586910386772373</v>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K27" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L27" t="n">
-        <v>0.006914777978546227</v>
+        <v>0.006624432781101586</v>
       </c>
       <c r="M27" t="n">
-        <v>11.59816652561221</v>
+        <v>11.50670162175557</v>
       </c>
       <c r="N27" t="n">
-        <v>243.1289960138746</v>
+        <v>240.8112922710927</v>
       </c>
       <c r="O27" t="n">
-        <v>15.59259426823755</v>
+        <v>15.51809563932033</v>
       </c>
       <c r="P27" t="n">
-        <v>343.4146044449065</v>
+        <v>343.4638433865378</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -26990,28 +27232,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2766445502852523</v>
+        <v>0.2615341990360503</v>
       </c>
       <c r="J28" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K28" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02052222793467429</v>
+        <v>0.01868438149875817</v>
       </c>
       <c r="M28" t="n">
-        <v>11.67469597435192</v>
+        <v>11.63004742452982</v>
       </c>
       <c r="N28" t="n">
-        <v>230.6332788283346</v>
+        <v>229.0837188223952</v>
       </c>
       <c r="O28" t="n">
-        <v>15.18661512083369</v>
+        <v>15.13551184540501</v>
       </c>
       <c r="P28" t="n">
-        <v>342.4840939292085</v>
+        <v>342.6314468447773</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27068,28 +27310,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2490764936266932</v>
+        <v>0.2329610596239063</v>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K29" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01506793717782728</v>
+        <v>0.01342416710858707</v>
       </c>
       <c r="M29" t="n">
-        <v>12.25016848008538</v>
+        <v>12.19508181640662</v>
       </c>
       <c r="N29" t="n">
-        <v>256.0504939516197</v>
+        <v>254.3413988371783</v>
       </c>
       <c r="O29" t="n">
-        <v>16.00157785818698</v>
+        <v>15.94808448802483</v>
       </c>
       <c r="P29" t="n">
-        <v>345.1872459419653</v>
+        <v>345.3444263311957</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27146,28 +27388,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3044702109741376</v>
+        <v>0.2830596551913176</v>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K30" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02230265760527073</v>
+        <v>0.01960410594594708</v>
       </c>
       <c r="M30" t="n">
-        <v>12.25592685820462</v>
+        <v>12.22004346063302</v>
       </c>
       <c r="N30" t="n">
-        <v>256.5931691599302</v>
+        <v>255.5157386065282</v>
       </c>
       <c r="O30" t="n">
-        <v>16.01852581107045</v>
+        <v>15.98485966802737</v>
       </c>
       <c r="P30" t="n">
-        <v>349.0688876476996</v>
+        <v>349.2777359060993</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -27224,28 +27466,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2542285351541154</v>
+        <v>0.2377940094445921</v>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K31" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0152487397456853</v>
+        <v>0.01358655729615321</v>
       </c>
       <c r="M31" t="n">
-        <v>12.25673772884167</v>
+        <v>12.19397438016286</v>
       </c>
       <c r="N31" t="n">
-        <v>263.541394717407</v>
+        <v>261.7933696448198</v>
       </c>
       <c r="O31" t="n">
-        <v>16.23395807304574</v>
+        <v>16.18002996427447</v>
       </c>
       <c r="P31" t="n">
-        <v>348.6853601965711</v>
+        <v>348.8456678433602</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -27302,28 +27544,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2498489975227309</v>
+        <v>0.2314274202312074</v>
       </c>
       <c r="J32" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K32" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01409390515340925</v>
+        <v>0.01230822144836308</v>
       </c>
       <c r="M32" t="n">
-        <v>12.58972574319993</v>
+        <v>12.52933401549884</v>
       </c>
       <c r="N32" t="n">
-        <v>275.7192485343888</v>
+        <v>274.0709670305371</v>
       </c>
       <c r="O32" t="n">
-        <v>16.60479594979682</v>
+        <v>16.55508885601455</v>
       </c>
       <c r="P32" t="n">
-        <v>348.0808951708941</v>
+        <v>348.2605835594794</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -27380,28 +27622,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2462039048361003</v>
+        <v>0.2282724763858346</v>
       </c>
       <c r="J33" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K33" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01377038974354583</v>
+        <v>0.01205022343239681</v>
       </c>
       <c r="M33" t="n">
-        <v>12.4739084816488</v>
+        <v>12.41967245064323</v>
       </c>
       <c r="N33" t="n">
-        <v>274.112812258673</v>
+        <v>272.4295008430882</v>
       </c>
       <c r="O33" t="n">
-        <v>16.55635262546292</v>
+        <v>16.5054385231986</v>
       </c>
       <c r="P33" t="n">
-        <v>350.8077766800945</v>
+        <v>350.9826966714656</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -27458,28 +27700,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1847242425167134</v>
+        <v>0.1638773411346865</v>
       </c>
       <c r="J34" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K34" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L34" t="n">
-        <v>0.007376374804096142</v>
+        <v>0.005902174967300833</v>
       </c>
       <c r="M34" t="n">
-        <v>13.20704766912633</v>
+        <v>13.15277733256241</v>
       </c>
       <c r="N34" t="n">
-        <v>289.9326181315621</v>
+        <v>288.4444109573491</v>
       </c>
       <c r="O34" t="n">
-        <v>17.02740785121335</v>
+        <v>16.98365128461336</v>
       </c>
       <c r="P34" t="n">
-        <v>356.2678299872622</v>
+        <v>356.4711631066547</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -27517,7 +27759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI201"/>
+  <dimension ref="A1:AI203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63021,6 +63263,360 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-34.426236931097264,172.96361691299617</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>-34.42610617590685,172.96451272981807</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-34.42605188529477,172.9654100780543</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-34.4259557555915,172.96630658659038</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-34.42587396300307,172.9672033816165</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-34.425707951220396,172.96809848543492</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-34.425589928352174,172.9689831455718</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-34.42538319074229,172.9697786895725</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-34.425186555754,172.97060471890066</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-34.424957766225575,172.97146547468049</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-34.42469264459634,172.97230617636168</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-34.42443424646045,172.97315059064985</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-34.4241717464559,172.9739927418264</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-34.423909821922464,172.97483605165448</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>-34.423607927346694,172.9756646083783</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>-34.42331331873211,172.97650312734433</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>-34.422945416914445,172.9772829008123</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>-34.42257149270323,172.9780584990771</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>-34.42221234508368,172.97884434559575</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>-34.42182684532626,172.97961191869967</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>-34.42140045010812,172.9803511324928</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>-34.42099659339397,172.98111538181004</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>-34.420563482272364,172.98185672413098</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>-34.420095639679054,172.98256062841705</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>-34.41963795329474,172.98326813053487</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>-34.419156518399284,172.98395103750784</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>-34.41869930518872,172.98465903574515</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>-34.418201715041135,172.98532521519877</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>-34.4176928950083,172.98599330302864</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>-34.41714572947408,172.98661533091567</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>-34.41661503540837,172.98724428753198</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>-34.41605308874964,172.98783111921915</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>-34.41550319736102,172.98843354559892</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>-34.4261647045371,172.96361546591453</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>-34.42604711424181,172.96451154609426</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>-34.42603439222292,172.9654097273345</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-34.42593357365662,172.9663061417109</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-34.4258551173769,172.9672030035202</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-34.42568991712948,172.96809812349701</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-34.42558812999457,172.96898297881637</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-34.425380594179984,172.96977777246977</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-34.425165807032656,172.97059326566776</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-34.424949401149824,172.97146085712646</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-34.42470027155839,172.97231038652214</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-34.42442776765906,172.9731470142457</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-34.42415919893449,172.97398581531218</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-34.42388233269674,172.9748206673077</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>-34.42358601552171,172.97565082471579</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>-34.42329478719443,172.97649027648922</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>-34.42292704181245,172.97727015834852</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>-34.42258439433396,172.9780674459538</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>-34.422223370082385,172.9788519911428</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>-34.42184021603285,172.979621190995</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>-34.42141859043538,172.98036371248622</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>-34.42099689473853,172.98111562109182</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>-34.42056425610034,172.98185747315242</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>-34.420085648681436,172.98255028003217</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>-34.41962796233588,172.98325778215076</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>-34.41914392709989,172.98393799571747</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>-34.41868739824534,172.9846467027485</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>-34.41820137288882,172.98532486080262</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>-34.41770258076511,172.98600438416815</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>-34.41715185871679,172.98662316439413</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>-34.41662118780948,172.98725224397742</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>-34.41606440912393,172.98784575903179</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>-34.415504920019906,172.98843577338957</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI203"/>
+  <dimension ref="A1:AI205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22992,6 +22992,228 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="C204" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>338.13</v>
+      </c>
+      <c r="E204" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="F204" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="G204" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="H204" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="I204" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="J204" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="K204" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="L204" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="M204" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="N204" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="O204" t="n">
+        <v>353.61</v>
+      </c>
+      <c r="P204" t="n">
+        <v>350.82</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>342.04</v>
+      </c>
+      <c r="R204" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="S204" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="T204" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="U204" t="n">
+        <v>338.42</v>
+      </c>
+      <c r="V204" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="W204" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="X204" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>344.49</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>341.31</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>341.92</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>345.62</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>344.18</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="C205" t="n">
+        <v>343.44</v>
+      </c>
+      <c r="D205" t="n">
+        <v>343.79</v>
+      </c>
+      <c r="E205" t="n">
+        <v>350.43</v>
+      </c>
+      <c r="F205" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="G205" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="H205" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="I205" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="J205" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="K205" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="L205" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="M205" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="N205" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="O205" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="P205" t="n">
+        <v>347.86</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>339.81</v>
+      </c>
+      <c r="R205" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="S205" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="T205" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="U205" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="V205" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="W205" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="X205" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>344.81</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>346.31</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>350.39</v>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23003,7 +23225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25036,6 +25258,26 @@
       </c>
       <c r="B203" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -25204,28 +25446,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1909341003835472</v>
+        <v>-0.17388977109876</v>
       </c>
       <c r="J2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K2" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005001233195449317</v>
+        <v>0.004223913502376164</v>
       </c>
       <c r="M2" t="n">
-        <v>17.28592745165724</v>
+        <v>17.1946707971389</v>
       </c>
       <c r="N2" t="n">
-        <v>445.8580181868986</v>
+        <v>442.4791571848254</v>
       </c>
       <c r="O2" t="n">
-        <v>21.11535029751812</v>
+        <v>21.03518854645295</v>
       </c>
       <c r="P2" t="n">
-        <v>326.1048804913867</v>
+        <v>325.9327123322251</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25282,28 +25524,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1549860122205227</v>
+        <v>-0.1261843949375748</v>
       </c>
       <c r="J3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00432490911610206</v>
+        <v>0.002904987510225943</v>
       </c>
       <c r="M3" t="n">
-        <v>14.99738635636374</v>
+        <v>14.96490874017647</v>
       </c>
       <c r="N3" t="n">
-        <v>344.3084742424248</v>
+        <v>343.5774190250816</v>
       </c>
       <c r="O3" t="n">
-        <v>18.55555103580664</v>
+        <v>18.53584147065036</v>
       </c>
       <c r="P3" t="n">
-        <v>328.4312790355247</v>
+        <v>328.1435523811389</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25360,28 +25602,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2682810336673622</v>
+        <v>-0.2443548456368002</v>
       </c>
       <c r="J4" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01600511749631095</v>
+        <v>0.01348265820596917</v>
       </c>
       <c r="M4" t="n">
-        <v>13.9592030319116</v>
+        <v>13.91028630847316</v>
       </c>
       <c r="N4" t="n">
-        <v>275.5091088384936</v>
+        <v>274.6579344671483</v>
       </c>
       <c r="O4" t="n">
-        <v>16.59846706290956</v>
+        <v>16.57280707868007</v>
       </c>
       <c r="P4" t="n">
-        <v>334.4390176249785</v>
+        <v>334.1999841717014</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25438,28 +25680,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2975087553539028</v>
+        <v>-0.2740832106081587</v>
       </c>
       <c r="J5" t="n">
+        <v>204</v>
+      </c>
+      <c r="K5" t="n">
         <v>202</v>
       </c>
-      <c r="K5" t="n">
-        <v>200</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02554895120994716</v>
+        <v>0.02200657812425288</v>
       </c>
       <c r="M5" t="n">
-        <v>12.23822625684711</v>
+        <v>12.19725454633034</v>
       </c>
       <c r="N5" t="n">
-        <v>213.2103546961586</v>
+        <v>212.8853873760484</v>
       </c>
       <c r="O5" t="n">
-        <v>14.60172437406482</v>
+        <v>14.59059242717884</v>
       </c>
       <c r="P5" t="n">
-        <v>343.5581127684342</v>
+        <v>343.3268958373497</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25516,28 +25758,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3800893559768347</v>
+        <v>-0.3632122715716781</v>
       </c>
       <c r="J6" t="n">
+        <v>204</v>
+      </c>
+      <c r="K6" t="n">
         <v>202</v>
       </c>
-      <c r="K6" t="n">
-        <v>200</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04574606353395072</v>
+        <v>0.0425343460804688</v>
       </c>
       <c r="M6" t="n">
-        <v>11.29984202985637</v>
+        <v>11.24789095631312</v>
       </c>
       <c r="N6" t="n">
-        <v>190.3283519452802</v>
+        <v>189.3660152342575</v>
       </c>
       <c r="O6" t="n">
-        <v>13.79595418756094</v>
+        <v>13.76103249157771</v>
       </c>
       <c r="P6" t="n">
-        <v>356.1727510058079</v>
+        <v>356.0061761513325</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25594,28 +25836,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3369868277604319</v>
+        <v>-0.317773226935865</v>
       </c>
       <c r="J7" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04429705191939004</v>
+        <v>0.04002586328964108</v>
       </c>
       <c r="M7" t="n">
-        <v>10.06352960862645</v>
+        <v>10.02869048859632</v>
       </c>
       <c r="N7" t="n">
-        <v>154.3477410959965</v>
+        <v>154.0334284131325</v>
       </c>
       <c r="O7" t="n">
-        <v>12.42367663358945</v>
+        <v>12.41102044205602</v>
       </c>
       <c r="P7" t="n">
-        <v>369.0581100245476</v>
+        <v>368.8679654375736</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25672,28 +25914,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3282443165540106</v>
+        <v>-0.3234079873001689</v>
       </c>
       <c r="J8" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K8" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05058106341125801</v>
+        <v>0.05004990922596764</v>
       </c>
       <c r="M8" t="n">
-        <v>9.094589534757111</v>
+        <v>9.02297793177326</v>
       </c>
       <c r="N8" t="n">
-        <v>127.4062372175084</v>
+        <v>126.2584711588647</v>
       </c>
       <c r="O8" t="n">
-        <v>11.28743714124284</v>
+        <v>11.23647948242085</v>
       </c>
       <c r="P8" t="n">
-        <v>386.3122056563066</v>
+        <v>386.2643737565521</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25750,28 +25992,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2347790344271724</v>
+        <v>-0.2239479620401701</v>
       </c>
       <c r="J9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K9" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02949129107207538</v>
+        <v>0.02732836742178535</v>
       </c>
       <c r="M9" t="n">
-        <v>8.828036369040619</v>
+        <v>8.786885746323307</v>
       </c>
       <c r="N9" t="n">
-        <v>114.274834491694</v>
+        <v>113.529399314801</v>
       </c>
       <c r="O9" t="n">
-        <v>10.68994080861508</v>
+        <v>10.65501756520378</v>
       </c>
       <c r="P9" t="n">
-        <v>395.2762368014957</v>
+        <v>395.1690382073668</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25828,28 +26070,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.203913284374073</v>
+        <v>-0.1932141977665054</v>
       </c>
       <c r="J10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02606852887101696</v>
+        <v>0.02382738910427795</v>
       </c>
       <c r="M10" t="n">
-        <v>7.803311852895753</v>
+        <v>7.777703610253251</v>
       </c>
       <c r="N10" t="n">
-        <v>97.86541478903686</v>
+        <v>97.27243374527009</v>
       </c>
       <c r="O10" t="n">
-        <v>9.892695021531638</v>
+        <v>9.862678832105916</v>
       </c>
       <c r="P10" t="n">
-        <v>384.9432994180783</v>
+        <v>384.8374071414393</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25906,28 +26148,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2548678886129119</v>
+        <v>-0.2485502782806558</v>
       </c>
       <c r="J11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04636897291626241</v>
+        <v>0.04496017962480614</v>
       </c>
       <c r="M11" t="n">
-        <v>7.00451089366637</v>
+        <v>6.977497786174347</v>
       </c>
       <c r="N11" t="n">
-        <v>84.16072421918295</v>
+        <v>83.46098352547307</v>
       </c>
       <c r="O11" t="n">
-        <v>9.173915424680072</v>
+        <v>9.135698305300645</v>
       </c>
       <c r="P11" t="n">
-        <v>377.6890640560437</v>
+        <v>377.6265365919008</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25984,28 +26226,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.252286720084098</v>
+        <v>-0.2505060040014457</v>
       </c>
       <c r="J12" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K12" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04742895817209591</v>
+        <v>0.04762527623432589</v>
       </c>
       <c r="M12" t="n">
-        <v>6.950283036249037</v>
+        <v>6.906452941262349</v>
       </c>
       <c r="N12" t="n">
-        <v>81.51730955222072</v>
+        <v>80.78614285009353</v>
       </c>
       <c r="O12" t="n">
-        <v>9.028693679166478</v>
+        <v>8.988111194800247</v>
       </c>
       <c r="P12" t="n">
-        <v>370.6573030734154</v>
+        <v>370.6399125748178</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26062,28 +26304,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2480714090305479</v>
+        <v>-0.2446909441499217</v>
       </c>
       <c r="J13" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K13" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04924218140556658</v>
+        <v>0.04878949229205842</v>
       </c>
       <c r="M13" t="n">
-        <v>6.87009562372868</v>
+        <v>6.83285433840314</v>
       </c>
       <c r="N13" t="n">
-        <v>75.76930698949081</v>
+        <v>75.14781808241139</v>
       </c>
       <c r="O13" t="n">
-        <v>8.70455667966444</v>
+        <v>8.668784117880165</v>
       </c>
       <c r="P13" t="n">
-        <v>364.7861064533545</v>
+        <v>364.7530604895017</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26140,28 +26382,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1450941751337739</v>
+        <v>-0.146073406366618</v>
       </c>
       <c r="J14" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K14" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02131936179405369</v>
+        <v>0.02200168231087618</v>
       </c>
       <c r="M14" t="n">
-        <v>6.357926691261999</v>
+        <v>6.314267938001981</v>
       </c>
       <c r="N14" t="n">
-        <v>61.62742458550377</v>
+        <v>61.0597151278567</v>
       </c>
       <c r="O14" t="n">
-        <v>7.850313661600011</v>
+        <v>7.814071610105496</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5274555719368</v>
+        <v>359.5370798634743</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26218,28 +26460,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1533996465818853</v>
+        <v>-0.156822468068497</v>
       </c>
       <c r="J15" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K15" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02283665276355407</v>
+        <v>0.02427590692062931</v>
       </c>
       <c r="M15" t="n">
-        <v>6.665875569365885</v>
+        <v>6.620591649045422</v>
       </c>
       <c r="N15" t="n">
-        <v>64.208230964854</v>
+        <v>63.6353410366865</v>
       </c>
       <c r="O15" t="n">
-        <v>8.013003866519346</v>
+        <v>7.977176257090381</v>
       </c>
       <c r="P15" t="n">
-        <v>358.3595488992343</v>
+        <v>358.3930918989098</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26296,28 +26538,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.131351098623091</v>
+        <v>-0.1400615635080231</v>
       </c>
       <c r="J16" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K16" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01932346780902905</v>
+        <v>0.02222518916372795</v>
       </c>
       <c r="M16" t="n">
-        <v>6.274593663671562</v>
+        <v>6.260506431546148</v>
       </c>
       <c r="N16" t="n">
-        <v>55.83614163812072</v>
+        <v>55.55991346512316</v>
       </c>
       <c r="O16" t="n">
-        <v>7.472358505727675</v>
+        <v>7.453852256727601</v>
       </c>
       <c r="P16" t="n">
-        <v>357.9702255296162</v>
+        <v>358.0555483548736</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26374,28 +26616,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1493580158482989</v>
+        <v>-0.1629997498871833</v>
       </c>
       <c r="J17" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K17" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02464164332352392</v>
+        <v>0.02944438542205674</v>
       </c>
       <c r="M17" t="n">
-        <v>6.17868840104878</v>
+        <v>6.197421453877942</v>
       </c>
       <c r="N17" t="n">
-        <v>56.30654502099467</v>
+        <v>56.37960774836155</v>
       </c>
       <c r="O17" t="n">
-        <v>7.503768721182355</v>
+        <v>7.508635545048218</v>
       </c>
       <c r="P17" t="n">
-        <v>352.9425948393275</v>
+        <v>353.0761984583172</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26452,28 +26694,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.07353335234923057</v>
+        <v>-0.08545782612268582</v>
       </c>
       <c r="J18" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K18" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006462071626980093</v>
+        <v>0.00879582471660767</v>
       </c>
       <c r="M18" t="n">
-        <v>5.98129115710902</v>
+        <v>5.982609429717549</v>
       </c>
       <c r="N18" t="n">
-        <v>53.01376898643215</v>
+        <v>52.98104015082068</v>
       </c>
       <c r="O18" t="n">
-        <v>7.281055485740523</v>
+        <v>7.278807605014758</v>
       </c>
       <c r="P18" t="n">
-        <v>348.0456305615149</v>
+        <v>348.1624236965333</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26530,28 +26772,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.002166606685495277</v>
+        <v>-0.01477882290682887</v>
       </c>
       <c r="J19" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K19" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L19" t="n">
-        <v>4.391311144824606e-06</v>
+        <v>0.0002066344143168974</v>
       </c>
       <c r="M19" t="n">
-        <v>6.710148083682878</v>
+        <v>6.697461570379408</v>
       </c>
       <c r="N19" t="n">
-        <v>68.16654887252552</v>
+        <v>68.03267206111397</v>
       </c>
       <c r="O19" t="n">
-        <v>8.256303584082016</v>
+        <v>8.248192048025674</v>
       </c>
       <c r="P19" t="n">
-        <v>344.1815226859302</v>
+        <v>344.3050435924617</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26608,28 +26850,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.03442179149784106</v>
+        <v>-0.04790759793715292</v>
       </c>
       <c r="J20" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K20" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0008162968738345544</v>
+        <v>0.001600334014536187</v>
       </c>
       <c r="M20" t="n">
-        <v>7.662722396755258</v>
+        <v>7.641752165535361</v>
       </c>
       <c r="N20" t="n">
-        <v>92.48502417024368</v>
+        <v>92.17917667451226</v>
       </c>
       <c r="O20" t="n">
-        <v>9.616913443004657</v>
+        <v>9.60099873317939</v>
       </c>
       <c r="P20" t="n">
-        <v>345.5201407969097</v>
+        <v>345.6521889100699</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26686,28 +26928,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.02656520695884692</v>
+        <v>-0.04096392626699839</v>
       </c>
       <c r="J21" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K21" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005011529947943627</v>
+        <v>0.00120473638471752</v>
       </c>
       <c r="M21" t="n">
-        <v>7.400845259937906</v>
+        <v>7.383563856846068</v>
       </c>
       <c r="N21" t="n">
-        <v>89.75231128445915</v>
+        <v>89.56077448991759</v>
       </c>
       <c r="O21" t="n">
-        <v>9.473769644891053</v>
+        <v>9.463655450718692</v>
       </c>
       <c r="P21" t="n">
-        <v>348.3086440050173</v>
+        <v>348.4496251601063</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -26764,28 +27006,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.08357515975812516</v>
+        <v>-0.09577257459957859</v>
       </c>
       <c r="J22" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K22" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004046681729431123</v>
+        <v>0.005386215103469372</v>
       </c>
       <c r="M22" t="n">
-        <v>7.664040448003522</v>
+        <v>7.643346156308642</v>
       </c>
       <c r="N22" t="n">
-        <v>109.6229870270119</v>
+        <v>109.0393734341833</v>
       </c>
       <c r="O22" t="n">
-        <v>10.47009966652715</v>
+        <v>10.44219198416613</v>
       </c>
       <c r="P22" t="n">
-        <v>354.1664795818755</v>
+        <v>354.2859135197693</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -26842,28 +27084,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1037889606696822</v>
+        <v>-0.1153532418302176</v>
       </c>
       <c r="J23" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K23" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005695638069562414</v>
+        <v>0.007136114432520491</v>
       </c>
       <c r="M23" t="n">
-        <v>8.011274071501196</v>
+        <v>7.982885626919447</v>
       </c>
       <c r="N23" t="n">
-        <v>119.9186008862487</v>
+        <v>119.1839455222324</v>
       </c>
       <c r="O23" t="n">
-        <v>10.95073517560573</v>
+        <v>10.91713998821268</v>
       </c>
       <c r="P23" t="n">
-        <v>360.7559361613238</v>
+        <v>360.8691725735276</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -26920,28 +27162,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1053823674881417</v>
+        <v>-0.1171489761321931</v>
       </c>
       <c r="J24" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K24" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005292621210375659</v>
+        <v>0.006636285820468268</v>
       </c>
       <c r="M24" t="n">
-        <v>8.695136183813684</v>
+        <v>8.668471182670066</v>
       </c>
       <c r="N24" t="n">
-        <v>133.0968248883595</v>
+        <v>132.2484058289167</v>
       </c>
       <c r="O24" t="n">
-        <v>11.53675972222528</v>
+        <v>11.49993068800489</v>
       </c>
       <c r="P24" t="n">
-        <v>359.140678702891</v>
+        <v>359.2558971441463</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -26998,28 +27240,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07020124514714997</v>
+        <v>-0.07746520723776761</v>
       </c>
       <c r="J25" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K25" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002256168315304063</v>
+        <v>0.002795813668374225</v>
       </c>
       <c r="M25" t="n">
-        <v>8.926096754100444</v>
+        <v>8.872661078167456</v>
       </c>
       <c r="N25" t="n">
-        <v>138.9774863636616</v>
+        <v>137.7905662994509</v>
       </c>
       <c r="O25" t="n">
-        <v>11.78887129303148</v>
+        <v>11.73842264954925</v>
       </c>
       <c r="P25" t="n">
-        <v>353.6323708878659</v>
+        <v>353.703509061427</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27076,28 +27318,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>0.006149479320782433</v>
+        <v>-0.0002202804173813114</v>
       </c>
       <c r="J26" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K26" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L26" t="n">
-        <v>1.227854172158871e-05</v>
+        <v>1.605181221275842e-08</v>
       </c>
       <c r="M26" t="n">
-        <v>10.33426721771347</v>
+        <v>10.2609659697416</v>
       </c>
       <c r="N26" t="n">
-        <v>196.3956365009445</v>
+        <v>194.6067700858058</v>
       </c>
       <c r="O26" t="n">
-        <v>14.01412275174385</v>
+        <v>13.95015304883089</v>
       </c>
       <c r="P26" t="n">
-        <v>347.528538541528</v>
+        <v>347.5909228748081</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27154,28 +27396,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1586910386772373</v>
+        <v>0.1523142527835257</v>
       </c>
       <c r="J27" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K27" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L27" t="n">
-        <v>0.006624432781101586</v>
+        <v>0.006220930129002711</v>
       </c>
       <c r="M27" t="n">
-        <v>11.50670162175557</v>
+        <v>11.42283938106452</v>
       </c>
       <c r="N27" t="n">
-        <v>240.8112922710927</v>
+        <v>238.5864924126044</v>
       </c>
       <c r="O27" t="n">
-        <v>15.51809563932033</v>
+        <v>15.44624525289575</v>
       </c>
       <c r="P27" t="n">
-        <v>343.4638433865378</v>
+        <v>343.5262949913569</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27232,28 +27474,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2615341990360503</v>
+        <v>0.2474227377928113</v>
       </c>
       <c r="J28" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K28" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01868438149875817</v>
+        <v>0.01702865070506332</v>
       </c>
       <c r="M28" t="n">
-        <v>11.63004742452982</v>
+        <v>11.58234737768093</v>
       </c>
       <c r="N28" t="n">
-        <v>229.0837188223952</v>
+        <v>227.4940698941967</v>
       </c>
       <c r="O28" t="n">
-        <v>15.13551184540501</v>
+        <v>15.08290654662412</v>
       </c>
       <c r="P28" t="n">
-        <v>342.6314468447773</v>
+        <v>342.7696286492339</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27310,28 +27552,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2329610596239063</v>
+        <v>0.2161392925977152</v>
       </c>
       <c r="J29" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K29" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01342416710858707</v>
+        <v>0.01175755147062008</v>
       </c>
       <c r="M29" t="n">
-        <v>12.19508181640662</v>
+        <v>12.14338173236781</v>
       </c>
       <c r="N29" t="n">
-        <v>254.3413988371783</v>
+        <v>252.7809309469216</v>
       </c>
       <c r="O29" t="n">
-        <v>15.94808448802483</v>
+        <v>15.89908585255522</v>
       </c>
       <c r="P29" t="n">
-        <v>345.3444263311957</v>
+        <v>345.5091527503221</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27388,28 +27630,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2830596551913176</v>
+        <v>0.2620597664044241</v>
       </c>
       <c r="J30" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K30" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01960410594594708</v>
+        <v>0.01707740548974357</v>
       </c>
       <c r="M30" t="n">
-        <v>12.22004346063302</v>
+        <v>12.18485299830586</v>
       </c>
       <c r="N30" t="n">
-        <v>255.5157386065282</v>
+        <v>254.4651829129247</v>
       </c>
       <c r="O30" t="n">
-        <v>15.98485966802737</v>
+        <v>15.95196486057202</v>
       </c>
       <c r="P30" t="n">
-        <v>349.2777359060993</v>
+        <v>349.483364328216</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -27466,28 +27708,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2377940094445921</v>
+        <v>0.2216921294341698</v>
       </c>
       <c r="J31" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01358655729615321</v>
+        <v>0.01201904932558218</v>
       </c>
       <c r="M31" t="n">
-        <v>12.19397438016286</v>
+        <v>12.13273115910863</v>
       </c>
       <c r="N31" t="n">
-        <v>261.7933696448198</v>
+        <v>260.0813705433703</v>
       </c>
       <c r="O31" t="n">
-        <v>16.18002996427447</v>
+        <v>16.12703849264862</v>
       </c>
       <c r="P31" t="n">
-        <v>348.8456678433602</v>
+        <v>349.003338238049</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -27544,28 +27786,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2314274202312074</v>
+        <v>0.2141807109967349</v>
       </c>
       <c r="J32" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K32" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01230822144836308</v>
+        <v>0.01072647230200408</v>
       </c>
       <c r="M32" t="n">
-        <v>12.52933401549884</v>
+        <v>12.4659208280944</v>
       </c>
       <c r="N32" t="n">
-        <v>274.0709670305371</v>
+        <v>272.3644527555898</v>
       </c>
       <c r="O32" t="n">
-        <v>16.55508885601455</v>
+        <v>16.50346790088646</v>
       </c>
       <c r="P32" t="n">
-        <v>348.2605835594794</v>
+        <v>348.429464101398</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -27622,28 +27864,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2282724763858346</v>
+        <v>0.2096388110660978</v>
       </c>
       <c r="J33" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K33" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01205022343239681</v>
+        <v>0.01033587104692901</v>
       </c>
       <c r="M33" t="n">
-        <v>12.41967245064323</v>
+        <v>12.36856348460454</v>
       </c>
       <c r="N33" t="n">
-        <v>272.4295008430882</v>
+        <v>270.9033431581866</v>
       </c>
       <c r="O33" t="n">
-        <v>16.5054385231986</v>
+        <v>16.45914162883917</v>
       </c>
       <c r="P33" t="n">
-        <v>350.9826966714656</v>
+        <v>351.165157092307</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -27700,28 +27942,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1638773411346865</v>
+        <v>0.14512478335564</v>
       </c>
       <c r="J34" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K34" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L34" t="n">
-        <v>0.005902174967300833</v>
+        <v>0.004705630898053759</v>
       </c>
       <c r="M34" t="n">
-        <v>13.15277733256241</v>
+        <v>13.09363967532727</v>
       </c>
       <c r="N34" t="n">
-        <v>288.4444109573491</v>
+        <v>286.778836693416</v>
       </c>
       <c r="O34" t="n">
-        <v>16.98365128461336</v>
+        <v>16.9345456594919</v>
       </c>
       <c r="P34" t="n">
-        <v>356.4711631066547</v>
+        <v>356.6547805168499</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -27759,7 +28001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI203"/>
+  <dimension ref="A1:AI205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63617,6 +63859,360 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>-34.4261647045371,172.96361546591453</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>-34.42604711424181,172.96451154609426</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-34.42603439222292,172.9654097273345</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-34.42593357365662,172.9663061417109</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-34.4258551173769,172.9672030035202</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-34.42568991712948,172.96809812349701</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-34.42558812999457,172.96898297881637</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-34.425380594179984,172.96977777246977</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-34.425165807032656,172.97059326566776</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-34.424949401149824,172.97146085712646</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-34.42470027155839,172.97231038652214</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-34.42442776765906,172.9731470142457</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-34.424170188266984,172.97399188167094</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-34.42388928681654,172.9748245591802</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>-34.42359497218029,172.97565645891274</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>-34.42329251962219,172.97648870402213</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>-34.42293611207573,172.97727644824482</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>-34.4225884603023,172.97807026557615</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>-34.422230954655674,172.97885725084654</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>-34.4218454548475,172.9796248240004</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>-34.42142922441968,172.98037108696764</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>-34.42100563373029,172.98112256026386</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>-34.42056953220007,172.9818625801172</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>-34.420093928891845,172.98255885643317</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>-34.41963507918338,172.9832651536022</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>-34.419153302143584,172.98394770618057</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>-34.41869232525655,172.98465180605703</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>-34.41820588929939,172.98532953883193</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>-34.41770238443221,172.98600415955045</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>-34.41715117768986,172.9866222940076</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>-34.41661786551295,172.98724794749674</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>-34.41606570112306,172.9878474298802</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>-34.41550375107281,172.98843426167448</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>-34.42608887115655,172.96361394657174</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>-34.42599896320454,172.96451058104427</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>-34.42598335573463,172.96540870410132</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-34.4259110310398,172.96630568959787</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-34.42584528879672,172.96720280633133</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-34.42570704951586,172.96809846733802</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-34.42562032059556,172.96898596373998</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-34.425380594179984,172.96977777246977</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-34.425165807032656,172.97059326566776</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-34.424949401149824,172.97146085712646</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-34.424740046573,172.97233234274776</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-34.424475661580644,172.97317345248698</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-34.424200531944614,172.97400863207272</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-34.423911539999004,172.9748370131765</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-34.42361864334811,172.9756713492962</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>-34.423309956470085,172.9765007957542</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>-34.42295777123754,172.97729146808894</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>-34.42260464598327,172.9780814898446</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>-34.4222250902949,172.9788531840652</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>-34.421834429879205,172.9796171784224</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>-34.42142492391138,172.98036810464035</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>-34.421003298310126,172.98112070582982</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>-34.42056791419618,172.98186101398124</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>-34.42009974556822,172.98256488117866</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>-34.41964253818653,172.98327287945168</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>-34.419159666223905,172.98395429795602</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>-34.41869218839513,172.98465166429847</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>-34.41820924239196,172.98533301191458</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>-34.41769813055265,172.98599929283347</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>-34.417149815635945,172.9866205532345</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>-34.41661638893666,172.98724603794986</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>-34.4160633016961,172.987844326876</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>-34.415496737389844,172.98842519138475</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI205"/>
+  <dimension ref="A1:AI207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23134,7 +23134,7 @@
         <v>395.31</v>
       </c>
       <c r="J205" t="n">
-        <v>385.72</v>
+        <v>379.79</v>
       </c>
       <c r="K205" t="n">
         <v>374.56</v>
@@ -23209,6 +23209,228 @@
         <v>350.39</v>
       </c>
       <c r="AI205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="C206" t="n">
+        <v>349.48</v>
+      </c>
+      <c r="D206" t="n">
+        <v>348.69</v>
+      </c>
+      <c r="E206" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="F206" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="G206" t="n">
+        <v>370.46</v>
+      </c>
+      <c r="H206" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="I206" t="n">
+        <v>394.47</v>
+      </c>
+      <c r="J206" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="K206" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="L206" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="M206" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="N206" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="O206" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="P206" t="n">
+        <v>345.78</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="R206" t="n">
+        <v>335.75</v>
+      </c>
+      <c r="S206" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="T206" t="n">
+        <v>334.93</v>
+      </c>
+      <c r="U206" t="n">
+        <v>337.67</v>
+      </c>
+      <c r="V206" t="n">
+        <v>341.25</v>
+      </c>
+      <c r="W206" t="n">
+        <v>347.01</v>
+      </c>
+      <c r="X206" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>344.58</v>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="C207" t="n">
+        <v>349.36</v>
+      </c>
+      <c r="D207" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="E207" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="F207" t="n">
+        <v>358.05</v>
+      </c>
+      <c r="G207" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="H207" t="n">
+        <v>380.61</v>
+      </c>
+      <c r="I207" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="J207" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="K207" t="n">
+        <v>374.32</v>
+      </c>
+      <c r="L207" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="M207" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="N207" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="O207" t="n">
+        <v>347.19</v>
+      </c>
+      <c r="P207" t="n">
+        <v>345.65</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="R207" t="n">
+        <v>335.45</v>
+      </c>
+      <c r="S207" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="T207" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="U207" t="n">
+        <v>336.53</v>
+      </c>
+      <c r="V207" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="W207" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="X207" t="n">
+        <v>345.83</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>337.46</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>338.05</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>336.91</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>340.51</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>339.35</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>338.64</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>343.33</v>
+      </c>
+      <c r="AI207" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23225,7 +23447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25278,6 +25500,26 @@
       </c>
       <c r="B205" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -25446,28 +25688,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.17388977109876</v>
+        <v>-0.1448704583130645</v>
       </c>
       <c r="J2" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K2" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004223913502376164</v>
+        <v>0.002974105593638532</v>
       </c>
       <c r="M2" t="n">
-        <v>17.1946707971389</v>
+        <v>17.16068518017042</v>
       </c>
       <c r="N2" t="n">
-        <v>442.4791571848254</v>
+        <v>440.8404732764321</v>
       </c>
       <c r="O2" t="n">
-        <v>21.03518854645295</v>
+        <v>20.99620140112092</v>
       </c>
       <c r="P2" t="n">
-        <v>325.9327123322251</v>
+        <v>325.6382420228051</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25524,28 +25766,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1261843949375748</v>
+        <v>-0.08396751976793709</v>
       </c>
       <c r="J3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K3" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002904987510225943</v>
+        <v>0.001291371789082341</v>
       </c>
       <c r="M3" t="n">
-        <v>14.96490874017647</v>
+        <v>14.98966394866506</v>
       </c>
       <c r="N3" t="n">
-        <v>343.5774190250816</v>
+        <v>346.0117225572453</v>
       </c>
       <c r="O3" t="n">
-        <v>18.53584147065036</v>
+        <v>18.60139033936026</v>
       </c>
       <c r="P3" t="n">
-        <v>328.1435523811389</v>
+        <v>327.71975785513</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25602,28 +25844,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2443548456368002</v>
+        <v>-0.2081645015479678</v>
       </c>
       <c r="J4" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K4" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01348265820596917</v>
+        <v>0.009856524288122892</v>
       </c>
       <c r="M4" t="n">
-        <v>13.91028630847316</v>
+        <v>13.90644108913249</v>
       </c>
       <c r="N4" t="n">
-        <v>274.6579344671483</v>
+        <v>276.228401684972</v>
       </c>
       <c r="O4" t="n">
-        <v>16.57280707868007</v>
+        <v>16.62012038719852</v>
       </c>
       <c r="P4" t="n">
-        <v>334.1999841717014</v>
+        <v>333.8366855810612</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25680,28 +25922,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2740832106081587</v>
+        <v>-0.2465949171093907</v>
       </c>
       <c r="J5" t="n">
+        <v>206</v>
+      </c>
+      <c r="K5" t="n">
         <v>204</v>
       </c>
-      <c r="K5" t="n">
-        <v>202</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02200657812425288</v>
+        <v>0.01801712756467178</v>
       </c>
       <c r="M5" t="n">
-        <v>12.19725454633034</v>
+        <v>12.17329867725501</v>
       </c>
       <c r="N5" t="n">
-        <v>212.8853873760484</v>
+        <v>213.3151461879974</v>
       </c>
       <c r="O5" t="n">
-        <v>14.59059242717884</v>
+        <v>14.60531225917465</v>
       </c>
       <c r="P5" t="n">
-        <v>343.3268958373497</v>
+        <v>343.0542172748035</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25758,28 +26000,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3632122715716781</v>
+        <v>-0.3445300761566585</v>
       </c>
       <c r="J6" t="n">
+        <v>206</v>
+      </c>
+      <c r="K6" t="n">
         <v>204</v>
       </c>
-      <c r="K6" t="n">
-        <v>202</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0425343460804688</v>
+        <v>0.03891635621805611</v>
       </c>
       <c r="M6" t="n">
-        <v>11.24789095631312</v>
+        <v>11.20263937331507</v>
       </c>
       <c r="N6" t="n">
-        <v>189.3660152342575</v>
+        <v>188.6767509635913</v>
       </c>
       <c r="O6" t="n">
-        <v>13.76103249157771</v>
+        <v>13.73596559997117</v>
       </c>
       <c r="P6" t="n">
-        <v>356.0061761513325</v>
+        <v>355.8208477313158</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25836,28 +26078,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.317773226935865</v>
+        <v>-0.3001893890606628</v>
       </c>
       <c r="J7" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K7" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04002586328964108</v>
+        <v>0.03629951052044567</v>
       </c>
       <c r="M7" t="n">
-        <v>10.02869048859632</v>
+        <v>9.988411405219619</v>
       </c>
       <c r="N7" t="n">
-        <v>154.0334284131325</v>
+        <v>153.56553190039</v>
       </c>
       <c r="O7" t="n">
-        <v>12.41102044205602</v>
+        <v>12.3921560634294</v>
       </c>
       <c r="P7" t="n">
-        <v>368.8679654375736</v>
+        <v>368.6930408979378</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25914,28 +26156,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3234079873001689</v>
+        <v>-0.3195481766969322</v>
       </c>
       <c r="J8" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K8" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05004990922596764</v>
+        <v>0.04979199739098006</v>
       </c>
       <c r="M8" t="n">
-        <v>9.02297793177326</v>
+        <v>8.948973764969239</v>
       </c>
       <c r="N8" t="n">
-        <v>126.2584711588647</v>
+        <v>125.0816457814898</v>
       </c>
       <c r="O8" t="n">
-        <v>11.23647948242085</v>
+        <v>11.18399060181516</v>
       </c>
       <c r="P8" t="n">
-        <v>386.2643737565521</v>
+        <v>386.2259699210007</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25992,28 +26234,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2239479620401701</v>
+        <v>-0.2143027356213223</v>
       </c>
       <c r="J9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K9" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02732836742178535</v>
+        <v>0.02548294600892065</v>
       </c>
       <c r="M9" t="n">
-        <v>8.786885746323307</v>
+        <v>8.741109589275839</v>
       </c>
       <c r="N9" t="n">
-        <v>113.529399314801</v>
+        <v>112.734541572906</v>
       </c>
       <c r="O9" t="n">
-        <v>10.65501756520378</v>
+        <v>10.61765235694341</v>
       </c>
       <c r="P9" t="n">
-        <v>395.1690382073668</v>
+        <v>395.0730849146409</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26070,28 +26312,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1932141977665054</v>
+        <v>-0.1982670334192592</v>
       </c>
       <c r="J10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02382738910427795</v>
+        <v>0.02557268723542061</v>
       </c>
       <c r="M10" t="n">
-        <v>7.777703610253251</v>
+        <v>7.68438361228389</v>
       </c>
       <c r="N10" t="n">
-        <v>97.27243374527009</v>
+        <v>96.14702752060745</v>
       </c>
       <c r="O10" t="n">
-        <v>9.862678832105916</v>
+        <v>9.805459067305694</v>
       </c>
       <c r="P10" t="n">
-        <v>384.8374071414393</v>
+        <v>384.8874650690756</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26148,28 +26390,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2485502782806558</v>
+        <v>-0.2435629725249547</v>
       </c>
       <c r="J11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04496017962480614</v>
+        <v>0.04400181486353671</v>
       </c>
       <c r="M11" t="n">
-        <v>6.977497786174347</v>
+        <v>6.9419751544341</v>
       </c>
       <c r="N11" t="n">
-        <v>83.46098352547307</v>
+        <v>82.73147617078448</v>
       </c>
       <c r="O11" t="n">
-        <v>9.135698305300645</v>
+        <v>9.095684480608618</v>
       </c>
       <c r="P11" t="n">
-        <v>377.6265365919008</v>
+        <v>377.5769197301047</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26226,28 +26468,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2505060040014457</v>
+        <v>-0.2530906997039001</v>
       </c>
       <c r="J12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04762527623432589</v>
+        <v>0.04943292356827667</v>
       </c>
       <c r="M12" t="n">
-        <v>6.906452941262349</v>
+        <v>6.853211039948966</v>
       </c>
       <c r="N12" t="n">
-        <v>80.78614285009353</v>
+        <v>80.02723453305023</v>
       </c>
       <c r="O12" t="n">
-        <v>8.988111194800247</v>
+        <v>8.94579423712899</v>
       </c>
       <c r="P12" t="n">
-        <v>370.6399125748178</v>
+        <v>370.6653478218678</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26304,28 +26546,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2446909441499217</v>
+        <v>-0.2515687553060432</v>
       </c>
       <c r="J13" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04878949229205842</v>
+        <v>0.05224900012992717</v>
       </c>
       <c r="M13" t="n">
-        <v>6.83285433840314</v>
+        <v>6.802467324403489</v>
       </c>
       <c r="N13" t="n">
-        <v>75.14781808241139</v>
+        <v>74.58450882087459</v>
       </c>
       <c r="O13" t="n">
-        <v>8.668784117880165</v>
+        <v>8.636232327865814</v>
       </c>
       <c r="P13" t="n">
-        <v>364.7530604895017</v>
+        <v>364.8207492812055</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26382,28 +26624,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.146073406366618</v>
+        <v>-0.1557249892787198</v>
       </c>
       <c r="J14" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K14" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02200168231087618</v>
+        <v>0.02526569063234962</v>
       </c>
       <c r="M14" t="n">
-        <v>6.314267938001981</v>
+        <v>6.313349793013277</v>
       </c>
       <c r="N14" t="n">
-        <v>61.0597151278567</v>
+        <v>60.78419406790482</v>
       </c>
       <c r="O14" t="n">
-        <v>7.814071610105496</v>
+        <v>7.796421875957254</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5370798634743</v>
+        <v>359.6320744876818</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26460,28 +26702,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.156822468068497</v>
+        <v>-0.1684100125632116</v>
       </c>
       <c r="J15" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K15" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02427590692062931</v>
+        <v>0.02821188343572478</v>
       </c>
       <c r="M15" t="n">
-        <v>6.620591649045422</v>
+        <v>6.623094660635346</v>
       </c>
       <c r="N15" t="n">
-        <v>63.6353410366865</v>
+        <v>63.47376862334487</v>
       </c>
       <c r="O15" t="n">
-        <v>7.977176257090381</v>
+        <v>7.967042652286033</v>
       </c>
       <c r="P15" t="n">
-        <v>358.3930918989098</v>
+        <v>358.5071445390724</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26538,28 +26780,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1400615635080231</v>
+        <v>-0.154364082850253</v>
       </c>
       <c r="J16" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K16" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02222518916372795</v>
+        <v>0.02703533249542445</v>
       </c>
       <c r="M16" t="n">
-        <v>6.260506431546148</v>
+        <v>6.276182922340408</v>
       </c>
       <c r="N16" t="n">
-        <v>55.55991346512316</v>
+        <v>55.7156026995217</v>
       </c>
       <c r="O16" t="n">
-        <v>7.453852256727601</v>
+        <v>7.464288492516999</v>
       </c>
       <c r="P16" t="n">
-        <v>358.0555483548736</v>
+        <v>358.1963238098501</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26616,28 +26858,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1629997498871833</v>
+        <v>-0.1804025010012048</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K17" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02944438542205674</v>
+        <v>0.03585335824025349</v>
       </c>
       <c r="M17" t="n">
-        <v>6.197421453877942</v>
+        <v>6.237881522956222</v>
       </c>
       <c r="N17" t="n">
-        <v>56.37960774836155</v>
+        <v>56.86137077556375</v>
       </c>
       <c r="O17" t="n">
-        <v>7.508635545048218</v>
+        <v>7.540647901577407</v>
       </c>
       <c r="P17" t="n">
-        <v>353.0761984583172</v>
+        <v>353.2474871025794</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26694,28 +26936,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.08545782612268582</v>
+        <v>-0.1025757571327834</v>
       </c>
       <c r="J18" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K18" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00879582471660767</v>
+        <v>0.01262528226964121</v>
       </c>
       <c r="M18" t="n">
-        <v>5.982609429717549</v>
+        <v>6.015009851569139</v>
       </c>
       <c r="N18" t="n">
-        <v>52.98104015082068</v>
+        <v>53.46250861452201</v>
       </c>
       <c r="O18" t="n">
-        <v>7.278807605014758</v>
+        <v>7.311806111660922</v>
       </c>
       <c r="P18" t="n">
-        <v>348.1624236965333</v>
+        <v>348.3309111143565</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -26772,28 +27014,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01477882290682887</v>
+        <v>-0.03144221749117779</v>
       </c>
       <c r="J19" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K19" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002066344143168974</v>
+        <v>0.0009393259209909965</v>
       </c>
       <c r="M19" t="n">
-        <v>6.697461570379408</v>
+        <v>6.704145513780169</v>
       </c>
       <c r="N19" t="n">
-        <v>68.03267206111397</v>
+        <v>68.31575255569615</v>
       </c>
       <c r="O19" t="n">
-        <v>8.248192048025674</v>
+        <v>8.265334388619504</v>
       </c>
       <c r="P19" t="n">
-        <v>344.3050435924617</v>
+        <v>344.4690568336025</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -26850,28 +27092,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.04790759793715292</v>
+        <v>-0.06426787317747293</v>
       </c>
       <c r="J20" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K20" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001600334014536187</v>
+        <v>0.002902265254313474</v>
       </c>
       <c r="M20" t="n">
-        <v>7.641752165535361</v>
+        <v>7.632216027136323</v>
       </c>
       <c r="N20" t="n">
-        <v>92.17917667451226</v>
+        <v>92.19501679059279</v>
       </c>
       <c r="O20" t="n">
-        <v>9.60099873317939</v>
+        <v>9.601823617969286</v>
       </c>
       <c r="P20" t="n">
-        <v>345.6521889100699</v>
+        <v>345.8132211456563</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -26928,28 +27170,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.04096392626699839</v>
+        <v>-0.05804667797704295</v>
       </c>
       <c r="J21" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00120473638471752</v>
+        <v>0.002434954458892746</v>
       </c>
       <c r="M21" t="n">
-        <v>7.383563856846068</v>
+        <v>7.376015032744859</v>
       </c>
       <c r="N21" t="n">
-        <v>89.56077448991759</v>
+        <v>89.68588228742476</v>
       </c>
       <c r="O21" t="n">
-        <v>9.463655450718692</v>
+        <v>9.470263052704754</v>
       </c>
       <c r="P21" t="n">
-        <v>348.4496251601063</v>
+        <v>348.6177703371135</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27006,28 +27248,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09577257459957859</v>
+        <v>-0.1140779860782788</v>
       </c>
       <c r="J22" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005386215103469372</v>
+        <v>0.007688806185107033</v>
       </c>
       <c r="M22" t="n">
-        <v>7.643346156308642</v>
+        <v>7.649224284582424</v>
       </c>
       <c r="N22" t="n">
-        <v>109.0393734341833</v>
+        <v>109.1218280128538</v>
       </c>
       <c r="O22" t="n">
-        <v>10.44219198416613</v>
+        <v>10.44613938318141</v>
       </c>
       <c r="P22" t="n">
-        <v>354.2859135197693</v>
+        <v>354.4660924156079</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27084,28 +27326,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1153532418302176</v>
+        <v>-0.1342037709179355</v>
       </c>
       <c r="J23" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K23" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L23" t="n">
-        <v>0.007136114432520491</v>
+        <v>0.00971843085099322</v>
       </c>
       <c r="M23" t="n">
-        <v>7.982885626919447</v>
+        <v>7.987222931642543</v>
       </c>
       <c r="N23" t="n">
-        <v>119.1839455222324</v>
+        <v>119.2369750900241</v>
       </c>
       <c r="O23" t="n">
-        <v>10.91713998821268</v>
+        <v>10.91956844797559</v>
       </c>
       <c r="P23" t="n">
-        <v>360.8691725735276</v>
+        <v>361.0547171107696</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27162,28 +27404,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1171489761321931</v>
+        <v>-0.1337316777399679</v>
       </c>
       <c r="J24" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K24" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L24" t="n">
-        <v>0.006636285820468268</v>
+        <v>0.008732412313878446</v>
       </c>
       <c r="M24" t="n">
-        <v>8.668471182670066</v>
+        <v>8.665220326771715</v>
       </c>
       <c r="N24" t="n">
-        <v>132.2484058289167</v>
+        <v>131.8998262395906</v>
       </c>
       <c r="O24" t="n">
-        <v>11.49993068800489</v>
+        <v>11.4847649623138</v>
       </c>
       <c r="P24" t="n">
-        <v>359.2558971441463</v>
+        <v>359.4191182285437</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27240,28 +27482,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07746520723776761</v>
+        <v>-0.09239221464710314</v>
       </c>
       <c r="J25" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K25" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002795813668374225</v>
+        <v>0.004025531691745798</v>
       </c>
       <c r="M25" t="n">
-        <v>8.872661078167456</v>
+        <v>8.855201920607307</v>
       </c>
       <c r="N25" t="n">
-        <v>137.7905662994509</v>
+        <v>137.2191341737625</v>
       </c>
       <c r="O25" t="n">
-        <v>11.73842264954925</v>
+        <v>11.71405711842667</v>
       </c>
       <c r="P25" t="n">
-        <v>353.703509061427</v>
+        <v>353.850439915461</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27318,28 +27560,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0002202804173813114</v>
+        <v>-0.01473563453929834</v>
       </c>
       <c r="J26" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K26" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L26" t="n">
-        <v>1.605181221275842e-08</v>
+        <v>7.292063984210007e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>10.2609659697416</v>
+        <v>10.22532694860607</v>
       </c>
       <c r="N26" t="n">
-        <v>194.6067700858058</v>
+        <v>193.4525718126137</v>
       </c>
       <c r="O26" t="n">
-        <v>13.95015304883089</v>
+        <v>13.90872286777667</v>
       </c>
       <c r="P26" t="n">
-        <v>347.5909228748081</v>
+        <v>347.7338060939741</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27396,28 +27638,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1523142527835257</v>
+        <v>0.138244493431023</v>
       </c>
       <c r="J27" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K27" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L27" t="n">
-        <v>0.006220930129002711</v>
+        <v>0.005212900546800014</v>
       </c>
       <c r="M27" t="n">
-        <v>11.42283938106452</v>
+        <v>11.37455704662717</v>
       </c>
       <c r="N27" t="n">
-        <v>238.5864924126044</v>
+        <v>236.9547138855673</v>
       </c>
       <c r="O27" t="n">
-        <v>15.44624525289575</v>
+        <v>15.39333342345209</v>
       </c>
       <c r="P27" t="n">
-        <v>343.5262949913569</v>
+        <v>343.6647895185309</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27474,28 +27716,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2474227377928113</v>
+        <v>0.2279766301585226</v>
       </c>
       <c r="J28" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K28" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01702865070506332</v>
+        <v>0.0146845077650497</v>
       </c>
       <c r="M28" t="n">
-        <v>11.58234737768093</v>
+        <v>11.56132681893883</v>
       </c>
       <c r="N28" t="n">
-        <v>227.4940698941967</v>
+        <v>226.57685401872</v>
       </c>
       <c r="O28" t="n">
-        <v>15.08290654662412</v>
+        <v>15.05247003048736</v>
       </c>
       <c r="P28" t="n">
-        <v>342.7696286492339</v>
+        <v>342.9610380303698</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27552,28 +27794,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2161392925977152</v>
+        <v>0.1940377364615344</v>
       </c>
       <c r="J29" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K29" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01175755147062008</v>
+        <v>0.009613911154443211</v>
       </c>
       <c r="M29" t="n">
-        <v>12.14338173236781</v>
+        <v>12.11570742533865</v>
       </c>
       <c r="N29" t="n">
-        <v>252.7809309469216</v>
+        <v>251.9972441439717</v>
       </c>
       <c r="O29" t="n">
-        <v>15.89908585255522</v>
+        <v>15.87442106484428</v>
       </c>
       <c r="P29" t="n">
-        <v>345.5091527503221</v>
+        <v>345.7267010036519</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27630,28 +27872,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2620597664044241</v>
+        <v>0.237013615929211</v>
       </c>
       <c r="J30" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K30" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01707740548974357</v>
+        <v>0.01415819787091221</v>
       </c>
       <c r="M30" t="n">
-        <v>12.18485299830586</v>
+        <v>12.16646524715316</v>
       </c>
       <c r="N30" t="n">
-        <v>254.4651829129247</v>
+        <v>254.1351915611989</v>
       </c>
       <c r="O30" t="n">
-        <v>15.95196486057202</v>
+        <v>15.94161822279027</v>
       </c>
       <c r="P30" t="n">
-        <v>349.483364328216</v>
+        <v>349.729894420569</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -27708,28 +27950,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2216921294341698</v>
+        <v>0.1977736986592419</v>
       </c>
       <c r="J31" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K31" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01201904932558218</v>
+        <v>0.009697532902866346</v>
       </c>
       <c r="M31" t="n">
-        <v>12.13273115910863</v>
+        <v>12.10063892944684</v>
       </c>
       <c r="N31" t="n">
-        <v>260.0813705433703</v>
+        <v>259.5151014586275</v>
       </c>
       <c r="O31" t="n">
-        <v>16.12703849264862</v>
+        <v>16.10947241403726</v>
       </c>
       <c r="P31" t="n">
-        <v>349.003338238049</v>
+        <v>349.2387711801278</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -27786,28 +28028,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2141807109967349</v>
+        <v>0.1884127111488229</v>
       </c>
       <c r="J32" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K32" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01072647230200408</v>
+        <v>0.008408743250834294</v>
       </c>
       <c r="M32" t="n">
-        <v>12.4659208280944</v>
+        <v>12.43406714254506</v>
       </c>
       <c r="N32" t="n">
-        <v>272.3644527555898</v>
+        <v>271.982498523499</v>
       </c>
       <c r="O32" t="n">
-        <v>16.50346790088646</v>
+        <v>16.49189190249254</v>
       </c>
       <c r="P32" t="n">
-        <v>348.429464101398</v>
+        <v>348.6830975470776</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -27864,28 +28106,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2096388110660978</v>
+        <v>0.1805500577922408</v>
       </c>
       <c r="J33" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K33" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01033587104692901</v>
+        <v>0.007750348143129471</v>
       </c>
       <c r="M33" t="n">
-        <v>12.36856348460454</v>
+        <v>12.35728632981657</v>
       </c>
       <c r="N33" t="n">
-        <v>270.9033431581866</v>
+        <v>271.1527242440288</v>
       </c>
       <c r="O33" t="n">
-        <v>16.45914162883917</v>
+        <v>16.46671564836257</v>
       </c>
       <c r="P33" t="n">
-        <v>351.165157092307</v>
+        <v>351.45147438663</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -27942,28 +28184,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.14512478335564</v>
+        <v>0.117484776077845</v>
       </c>
       <c r="J34" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K34" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L34" t="n">
-        <v>0.004705630898053759</v>
+        <v>0.00311930712174513</v>
       </c>
       <c r="M34" t="n">
-        <v>13.09363967532727</v>
+        <v>13.06935409283163</v>
       </c>
       <c r="N34" t="n">
-        <v>286.778836693416</v>
+        <v>286.5940697746922</v>
       </c>
       <c r="O34" t="n">
-        <v>16.9345456594919</v>
+        <v>16.92908945497933</v>
       </c>
       <c r="P34" t="n">
-        <v>356.6547805168499</v>
+        <v>356.9268377052452</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -28001,7 +28243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI205"/>
+  <dimension ref="A1:AI207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64084,7 +64326,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>-34.425165807032656,172.97059326566776</t>
+          <t>-34.42521443940934,172.97062011060598</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -64208,6 +64450,360 @@
         </is>
       </c>
       <c r="AI205" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-34.42607814086837,172.96361373158763</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>-34.42594450023307,172.9645094894909</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-34.42593917220202,172.9654078182644</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-34.425898317003885,172.96630543460623</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-34.42584321487613,172.96720276472266</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-34.425705516618116,172.96809843657329</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-34.42561501544067,172.96898547181107</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-34.42538786455442,172.96978034035763</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-34.425221738365835,172.97062413961288</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-34.42495793024666,172.97146556522077</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-34.42474578729641,172.97233551168924</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-34.42450780955201,172.97319119872066</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-34.424230711599954,172.9740252919438</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-34.42394115636476,172.97485358799065</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>-34.42363527714057,172.9756818128139</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>-34.4233226235965,172.97650957988554</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>-34.42297286227696,172.97730193318347</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>-34.42261754761227,172.9780904367284</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>-34.422241588696174,172.97886462527813</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>-34.42185131919213,172.97962889079807</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>-34.421454480130585,172.98038860136845</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>-34.4210358435177,172.98114654827495</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>-34.420589159289165,172.9818815780317</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>-34.420123080702176,172.98258905104845</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>-34.4196638202937,172.98329492293797</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>-34.41918156413193,172.98397697934155</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>-34.418711075269435,172.9846712269867</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>-34.41822518668795,172.98534952678094</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>-34.41771350996243,172.98601688788946</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>-34.417174518336985,172.98665212453656</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>-34.41664653569649,172.98728502454495</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>-34.4161020001367,172.98789437278563</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>-34.41553248255647,172.98847141805263</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>-34.426042162843196,172.96361301075908</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>-34.42594558227887,172.96450951117737</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-34.425937458963,172.96540778391562</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-34.425891283707394,172.96630529354704</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-34.42582986964798,172.96720249698004</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-34.425699565368134,172.96809831713378</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-34.42560197734811,172.96898426283352</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-34.425380594179984,172.96977777246977</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-34.42521033887192,172.97061784711929</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-34.42495136940296,172.97146194360965</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-34.42473709420093,172.97233071300658</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-34.42449550803268,172.9731844080684</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-34.42422620105379,172.97402280201666</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-34.42394181087007,172.97485395428504</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>-34.42363631675257,172.9756824667839</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>-34.42332145071445,172.97650876653995</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>-34.4229752080343,172.97730355988244</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>-34.4226193460211,172.97809168386996</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>-34.42224753124802,172.97886874628483</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>-34.42186023299572,172.97963507233155</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>-34.42146261199978,172.98039424068241</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>-34.42104405515483,172.98115306870983</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>-34.42059387260403,172.9818861402562</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>-34.4201365617011,172.98260301429312</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>-34.419683186323404,172.98331498181142</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>-34.41919689266499,172.98399285631842</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>-34.41872243476476,172.9846829929556</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>-34.41823969394243,172.98536455318836</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>-34.4177262715984,172.98603148804722</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>-34.417189996215654,172.98667190606363</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>-34.416656502581674,172.98729791399683</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>-34.416110490411825,172.9879053526575</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>-34.41554017299448,172.98848136355429</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
